--- a/output/full_scan/batch_seq1_2026-09-24.xlsx
+++ b/output/full_scan/batch_seq1_2026-09-24.xlsx
@@ -527,21 +527,21 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>1456</v>
+        <v>1560</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>怡華</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>806.8719013740497</v>
+        <v>944.0849841339212</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>14.7</v>
+        <v>971</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -552,16 +552,16 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>58.61440385580091</v>
+        <v>76.76980525541725</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>17.18896284450348</v>
+        <v>31.41680151569321</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>1.283795586748832</v>
+        <v>1.008498413392119</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>0</v>
@@ -570,31 +570,31 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.034084376473057</v>
+        <v>24.49570838820415</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, hist_turn_positive, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>1303</v>
+        <v>1569</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>濱川</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>739.1887917528754</v>
+        <v>926.4164965297218</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>238</v>
+        <v>64.7</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -605,16 +605,16 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>58.09717154144598</v>
+        <v>79.89106156477303</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>23.99712455717697</v>
+        <v>53.06968872101748</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.7949632640336151</v>
+        <v>2.741649652972179</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>0</v>
@@ -623,31 +623,31 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>-1.694069482801263</v>
+        <v>1.590931852628519</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>1569</v>
+        <v>1456</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>濱川</t>
+          <t>怡華</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>726.4164965297218</v>
+        <v>921.8719013740496</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>64.7</v>
+        <v>14.7</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,16 +658,16 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>79.89106155882993</v>
+        <v>58.61440123410856</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>53.06968862381356</v>
+        <v>17.18896284450348</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>2.741649652972179</v>
+        <v>1.283795586748832</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>0</v>
@@ -676,11 +676,11 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>1.590931851712702</v>
+        <v>0.0340843764825968</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, hist_turn_positive, stronger_than_market, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -697,7 +697,7 @@
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>677.5532753969899</v>
+        <v>777.5532753969899</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>14.6</v>
@@ -711,16 +711,16 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>56.55433802277081</v>
+        <v>56.55433796133729</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>40.34462203951103</v>
+        <v>40.34462201169195</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>0.1895911116324685</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>0</v>
@@ -729,31 +729,31 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>-0.07519359716255231</v>
+        <v>-0.07519359721979239</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>台泥</t>
+          <t>亞泥</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>674.8965367352395</v>
+        <v>767.8038587209888</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>25.25</v>
+        <v>35.7</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,49 +764,49 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>58.5260150708354</v>
+        <v>60.93299628994088</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>31.75787814026875</v>
+        <v>26.89643561385643</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.6525081178999347</v>
+        <v>0.999049460502734</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M6" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.09325906349184911</v>
+        <v>0.008277293785017001</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>1459</v>
+        <v>1303</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>聯發</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>671.6496279305617</v>
+        <v>739.1887917528753</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>15.95</v>
+        <v>238</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,16 +817,16 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>68.29302352570363</v>
+        <v>58.09717153367886</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>48.45375431600296</v>
+        <v>23.99712451639491</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.1306458913668709</v>
+        <v>0.7949632640336151</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>0</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>-0.0569605197327308</v>
+        <v>-1.694069483020671</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>1560</v>
+        <v>1558</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>伸興</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>634.0849841339212</v>
+        <v>722.3165231280179</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>971</v>
+        <v>112</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,16 +870,16 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>76.76980522805776</v>
+        <v>75.4911544196669</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>31.41680127540721</v>
+        <v>45.93921653948664</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>1.008498413392119</v>
+        <v>0.3006969482605902</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>24.4957083904938</v>
+        <v>0.068229957271102</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>1563</v>
+        <v>1528</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>巧新</t>
+          <t>恩德</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>621.5406767295482</v>
+        <v>678.8243237025708</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>75.2</v>
+        <v>25.45</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,13 +923,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>60.7155307347053</v>
+        <v>65.72105385539237</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>34.27801523606057</v>
+        <v>37.09592352816865</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.4865206968699114</v>
+        <v>0.7737003345632983</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>-0.3412781365943997</v>
+        <v>0.4556074238322736</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>1558</v>
+        <v>1459</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>伸興</t>
+          <t>聯發</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>612.3165231280179</v>
+        <v>671.6496279305617</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>112</v>
+        <v>15.95</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,13 +976,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>75.49115443649396</v>
+        <v>68.29302356023521</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>45.93921660444961</v>
+        <v>48.45375435943801</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.3006969482605902</v>
+        <v>0.1306458913668709</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.06822995729016321</v>
+        <v>-0.0569605197490807</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>1326</v>
+        <v>1101</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>台化</t>
+          <t>台泥</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>579.4169711616026</v>
+        <v>664.8965367352395</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>67</v>
+        <v>25.25</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,13 +1029,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>51.6301768132593</v>
+        <v>58.52601509604765</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>28.2657964148142</v>
+        <v>31.75787821900792</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.5053244878320772</v>
+        <v>0.6525081178999347</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>-0.6345949732496039</v>
+        <v>0.09325906346322931</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>1102</v>
+        <v>1563</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>亞泥</t>
+          <t>巧新</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>577.8038587209887</v>
+        <v>641.5406767295482</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>35.7</v>
+        <v>75.2</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,16 +1082,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>60.93299615621425</v>
+        <v>60.71553075306982</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>26.89643557456393</v>
+        <v>34.27801528573151</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.999049460502734</v>
+        <v>0.4865206968699114</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0.008277293851799801</v>
+        <v>-0.3412781365943997</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>1315</v>
+        <v>1418</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>達新</t>
+          <t>東華</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>577.1855898676964</v>
+        <v>633.4806829561159</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>68.3</v>
+        <v>18.3</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,13 +1135,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>71.14387135523901</v>
+        <v>60.28988304091983</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>36.1196901843629</v>
+        <v>18.1143949937001</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.4134116033172695</v>
+        <v>1.438336874983999</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.1645810013341765</v>
+        <v>0.0821446360632689</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>1528</v>
+        <v>1304</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>恩德</t>
+          <t>台聚</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>573.8243237025707</v>
+        <v>617.5477520375175</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>25.45</v>
+        <v>12.5</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,16 +1188,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>65.7210538663099</v>
+        <v>53.53620395911947</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>37.09592351575316</v>
+        <v>21.43000304873751</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.7737003345632983</v>
+        <v>0.7923255890524106</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.4556074235651606</v>
+        <v>0.001400774055535</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>1301</v>
+        <v>1513</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>中興電</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>571.8785020357898</v>
+        <v>593.4770650471729</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>64.09999999999999</v>
+        <v>166</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,16 +1241,16 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>53.23083447421082</v>
+        <v>52.0899266163139</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>22.95163957634671</v>
+        <v>10.26933187518033</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.5460843204995706</v>
+        <v>0.6639548655403902</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>-0.3531246923832589</v>
+        <v>0.07017635764339759</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, kd_golden_cross, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>1434</v>
+        <v>1326</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>福懋</t>
+          <t>台化</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>548.9363619506373</v>
+        <v>579.4169711616026</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>17.95</v>
+        <v>67</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,13 +1294,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>51.93921025993143</v>
+        <v>51.63017679584309</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>23.12381040153035</v>
+        <v>28.26579655622348</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.7842704691768611</v>
+        <v>0.5053244878320772</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.0027103238468793</v>
+        <v>-0.6345949734404042</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>中石化</t>
+          <t>達新</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>533.0339090367421</v>
+        <v>577.1855898676964</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>8.859999999999999</v>
+        <v>68.3</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,13 +1347,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>60.70055982630819</v>
+        <v>71.14387127086208</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>41.10032596536318</v>
+        <v>36.11969021148665</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1.013911217114202</v>
+        <v>0.4134116033172695</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>0.0752580333208399</v>
+        <v>0.1645810012960185</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>1418</v>
+        <v>1301</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>東華</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>518.4806829561159</v>
+        <v>571.8785020357898</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>18.3</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,16 +1400,16 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>60.28988274620739</v>
+        <v>53.23083443494485</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>18.1143950705206</v>
+        <v>22.95163970565744</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>1.438336874983999</v>
+        <v>0.5460843204995706</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.0821446360632689</v>
+        <v>-0.3531246927553171</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>1323</v>
+        <v>1434</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>永裕</t>
+          <t>福懋</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>517.8517259030282</v>
+        <v>568.9363619506373</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>21.4</v>
+        <v>17.95</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,16 +1453,16 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>54.08287234028921</v>
+        <v>51.93921032324754</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>15.87081655812794</v>
+        <v>23.12381048549101</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.407092049387347</v>
+        <v>0.7842704691768611</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>-0.0417863745214966</v>
+        <v>0.002710323799178</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>1437</v>
+        <v>1516</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>勤益控</t>
+          <t>川飛</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>516.6223503294817</v>
+        <v>554.3395472298201</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>32.5</v>
+        <v>13.15</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,16 +1506,16 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>56.79220562504735</v>
+        <v>44.40915745656954</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>15.71171695642624</v>
+        <v>15.14464571268223</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>1.105566558177927</v>
+        <v>0.2270158080671501</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.0256783707207232</v>
+        <v>-0.0742537835436735</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>1304</v>
+        <v>1314</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>台聚</t>
+          <t>中石化</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>507.5477520375173</v>
+        <v>523.0339090367421</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>12.5</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,13 +1559,13 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>53.53620393211106</v>
+        <v>60.70055981570912</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>21.43000298465799</v>
+        <v>41.10032606681857</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.7923255890524106</v>
+        <v>1.013911217114202</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0.0014007741318533</v>
+        <v>0.07525803329222081</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>1310</v>
+        <v>1323</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>台苯</t>
+          <t>永裕</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>486.933335558725</v>
+        <v>517.8517259030282</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>8.9</v>
+        <v>21.4</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,13 +1612,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>55.48243560008004</v>
+        <v>54.08287234028921</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>28.35361320522339</v>
+        <v>15.87081660312091</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.6913980111746824</v>
+        <v>0.407092049387347</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.0247344407681289</v>
+        <v>-0.0417863745310384</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>1474</v>
+        <v>1437</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>弘裕</t>
+          <t>勤益控</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>482.0208685501955</v>
+        <v>516.6223503294817</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>10</v>
+        <v>32.5</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,13 +1665,13 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>49.68909401599443</v>
+        <v>56.79220562504735</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>21.08901593291356</v>
+        <v>15.71171700071069</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.7878205253041712</v>
+        <v>1.105566558177927</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.016444875030292</v>
+        <v>0.0256783707207232</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>1417</v>
+        <v>1308</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>嘉裕</t>
+          <t>亞聚</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>480.5219110088153</v>
+        <v>507.9661180047838</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>8.1</v>
+        <v>14.3</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,16 +1718,16 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>42.50966776336448</v>
+        <v>53.48114731366788</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>28.89237806275843</v>
+        <v>27.67049543656308</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>2.508345645706944</v>
+        <v>0.6537112824940586</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.0030644794712054</v>
+        <v>-0.0210725773042343</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, volume_break, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>1339</v>
+        <v>1310</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>昭輝</t>
+          <t>台苯</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>479.1652374272359</v>
+        <v>496.933335558725</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>42.4</v>
+        <v>8.9</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,16 +1771,16 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>39.6499231204531</v>
+        <v>55.48243554290518</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>20.79792205136283</v>
+        <v>28.35361327067837</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.5862350659408259</v>
+        <v>0.6913980111746824</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>0</v>
@@ -1789,11 +1789,11 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.0154544951394886</v>
+        <v>0.0247344407166157</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>476.2549857292478</v>
+        <v>496.2549857292478</v>
       </c>
       <c r="E26" s="2" t="n">
         <v>30.9</v>
@@ -1824,16 +1824,16 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>58.45887264106175</v>
+        <v>58.45887265302812</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>18.71366382222565</v>
+        <v>18.71366384816152</v>
       </c>
       <c r="J26" s="2" t="n">
         <v>0.7051406157625537</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>0.256122169547709</v>
+        <v>0.2561221695572497</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1852,21 +1852,21 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>1338</v>
+        <v>1217</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>廣華-KY</t>
+          <t>愛之味</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>462.5553278624379</v>
+        <v>486.5214865959584</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>14.75</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,16 +1877,16 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>53.5877447359882</v>
+        <v>48.82640971135586</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>34.09691415139294</v>
+        <v>12.27444449253986</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>1.795983580426009</v>
+        <v>1.531400252959722</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>0</v>
@@ -1895,48 +1895,48 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.09347685502592019</v>
+        <v>-0.0047325484036099</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross, williams_r_recovery</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>1441</v>
+        <v>1474</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>大東</t>
+          <t>弘裕</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>459.5380175104262</v>
+        <v>482.0208685501955</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>8.720000000000001</v>
+        <v>10</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G28" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>44.18436452915455</v>
+        <v>49.68909414829141</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>13.92977539138412</v>
+        <v>21.08901584924069</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>1.053801751042616</v>
+        <v>0.7878205253041712</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>-0.0102843300449644</v>
+        <v>0.0164448750207527</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>1531</v>
+        <v>1417</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>高林股</t>
+          <t>嘉裕</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>453.5311559828204</v>
+        <v>480.5219110088154</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>11.65</v>
+        <v>8.1</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,13 +1983,13 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>36.43831639683352</v>
+        <v>42.50966776336448</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>21.99582897601388</v>
+        <v>28.89237807896638</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>2.528985684292139</v>
+        <v>2.508345645706944</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.0305312778522719</v>
+        <v>0.0030644794712054</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, volume_break, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>1516</v>
+        <v>1339</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>川飛</t>
+          <t>昭輝</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>444.3395472298201</v>
+        <v>479.1652374272359</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>13.15</v>
+        <v>42.4</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,13 +2036,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>44.40915746517518</v>
+        <v>39.64992315276202</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>15.14464572725995</v>
+        <v>20.7979220757806</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.2270158080671501</v>
+        <v>0.5862350659408259</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>-0.0742537835627529</v>
+        <v>0.0154544951585713</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>1313</v>
+        <v>1342</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>聯成</t>
+          <t>八貫</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>438.2348018867109</v>
+        <v>464.7905662744497</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>12.15</v>
+        <v>101</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,16 +2089,16 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>54.70469485240641</v>
+        <v>46.10594759896849</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>22.30187228634395</v>
+        <v>17.46624579589394</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.5316251204259922</v>
+        <v>0.4436552810998709</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.0140783796872897</v>
+        <v>0.1259237989099998</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>1236</v>
+        <v>1338</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>宏亞</t>
+          <t>廣華-KY</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>432.6332392714445</v>
+        <v>462.555327862438</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>25.4</v>
+        <v>14.75</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>44.72683601849952</v>
+        <v>53.58774456843417</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>18.44940277684737</v>
+        <v>34.09691411825446</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.7415643761119077</v>
+        <v>1.795983580426009</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
@@ -2160,48 +2160,48 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>-0.1122256822632851</v>
+        <v>0.09347685506407941</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>1463</v>
+        <v>1441</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>強盛新</t>
+          <t>大東</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>426.0120453233021</v>
+        <v>459.5380175104262</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>17.75</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G33" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>57.08322833403364</v>
+        <v>44.18436452915455</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>17.18057317193536</v>
+        <v>13.92977534151037</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>1.201204532330209</v>
+        <v>1.053801751042616</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0.057406435019907</v>
+        <v>-0.0102843300146885</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>1521</v>
+        <v>1531</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>大億</t>
+          <t>高林股</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>419.1744451668981</v>
+        <v>453.5311559828204</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>25.8</v>
+        <v>11.65</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>55.02449397264758</v>
+        <v>36.43831637129214</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>23.67688713317039</v>
+        <v>21.99582902388497</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.9556686811682706</v>
+        <v>2.528985684292139</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.09503921673011941</v>
+        <v>0.0305312778618117</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>1108</v>
+        <v>1477</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>幸福</t>
+          <t>聚陽</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>417.1400563098596</v>
+        <v>452.6367410460276</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>11.05</v>
+        <v>191</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,49 +2301,49 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>23.48532287729083</v>
+        <v>37.29775235181029</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>55.30601202685524</v>
+        <v>27.13297728318202</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.7419841596453609</v>
+        <v>0.6178356628006788</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L35" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M35" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>0.0029094900209389</v>
+        <v>0.3779994403631903</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, invest_trust_buy_2d, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>1513</v>
+        <v>1216</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>統一</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>408.4770650471729</v>
+        <v>450.357076267617</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>166</v>
+        <v>74.5</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,49 +2354,49 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>52.08992665944872</v>
+        <v>43.20257755502521</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>10.26933188972841</v>
+        <v>8.542082484448462</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.6639548655403902</v>
+        <v>0.5435439067548555</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M36" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0.0701763573572146</v>
+        <v>-0.0541424029096032</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, invest_trust_buy_2d, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>1308</v>
+        <v>1402</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>亞聚</t>
+          <t>遠東新</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>397.9661180047838</v>
+        <v>439.1013201603901</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>14.3</v>
+        <v>28.15</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,49 +2407,49 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>53.48114725271591</v>
+        <v>49.42826946386565</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>27.67049530251504</v>
+        <v>13.55143727436524</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.6537112824940586</v>
+        <v>0.5977734942476089</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L37" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M37" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>-0.0210725772183781</v>
+        <v>-0.085750096914386</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, invest_trust_buy_2d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>1473</v>
+        <v>1313</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>台南</t>
+          <t>聯成</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>393.1758889026947</v>
+        <v>438.2348018867109</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>19.5</v>
+        <v>12.15</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,13 +2460,13 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>35.01010905681584</v>
+        <v>54.70469457080497</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>25.93105861491039</v>
+        <v>22.30187226707582</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>2.633623604883756</v>
+        <v>0.5316251204259922</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>-0.0464793443971832</v>
+        <v>0.0140783796872897</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>1307</v>
+        <v>1236</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>三芳</t>
+          <t>宏亞</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>391.6016108006584</v>
+        <v>432.6332392714445</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>30.7</v>
+        <v>25.4</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>49.18804482084398</v>
+        <v>44.72683621650541</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>12.27872900345378</v>
+        <v>18.44940284513235</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.4851515203636359</v>
+        <v>0.7415643761119077</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.0730598206525139</v>
+        <v>-0.112225682320523</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>1470</v>
+        <v>1463</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>大統新創</t>
+          <t>強盛新</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>382.6570718815006</v>
+        <v>426.0120453233021</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>23.7</v>
+        <v>17.75</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,16 +2566,16 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>50.9236547453937</v>
+        <v>57.08322859267743</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>9.806275757817808</v>
+        <v>17.18057315787357</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.0747420465119755</v>
+        <v>1.201204532330209</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.0961146082970504</v>
+        <v>0.0574064350294469</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>1217</v>
+        <v>1340</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>愛之味</t>
+          <t>勝悅-KY</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>376.5214865959585</v>
+        <v>422.7298085177963</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>9.949999999999999</v>
+        <v>5.21</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,16 +2619,16 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>48.82640988519249</v>
+        <v>50.7310841260519</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>12.27444457717151</v>
+        <v>12.38310166049494</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>1.531400252959722</v>
+        <v>0.7146941047175062</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-0.0047325484226886</v>
+        <v>0.0077391385755187</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross, williams_r_recovery</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>1416</v>
+        <v>1521</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>廣豐</t>
+          <t>大億</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>373.0861512182735</v>
+        <v>419.1744451668981</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>11.45</v>
+        <v>25.8</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,16 +2672,16 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>49.76664295203796</v>
+        <v>55.02449394882009</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>15.48193238684968</v>
+        <v>23.6768871309057</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.5075576072771187</v>
+        <v>0.9556686811682706</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>-0.0126520573252165</v>
+        <v>0.09503921675873719</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>1309</v>
+        <v>1108</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>台達化</t>
+          <t>幸福</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>372.9722255578732</v>
+        <v>417.1400563098596</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>13.8</v>
+        <v>11.05</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>52.30168122409392</v>
+        <v>23.48532294346204</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>27.2016278661996</v>
+        <v>55.30601209721097</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.3390727924063561</v>
+        <v>0.7419841596453609</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.0022935548910097</v>
+        <v>0.0029094900209389</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>1233</v>
+        <v>1473</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>天仁</t>
+          <t>台南</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>368.6379822865925</v>
+        <v>393.175888902694</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>28.1</v>
+        <v>19.5</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>48.27071861529384</v>
+        <v>35.0101092558788</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>11.96934114263774</v>
+        <v>25.931058593161</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.8735184449598299</v>
+        <v>2.633623604883756</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.0113185601569905</v>
+        <v>-0.0464793444735024</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>1341</v>
+        <v>1307</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>富林-KY</t>
+          <t>三芳</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>364.8107824047806</v>
+        <v>391.6016108006584</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>60</v>
+        <v>30.7</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>52.16489368515279</v>
+        <v>49.18804479547161</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>10.57232560421675</v>
+        <v>12.27872906767675</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.3884383752219517</v>
+        <v>0.4851515203636359</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>1.714778827300275</v>
+        <v>0.0730598205857405</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>1321</v>
+        <v>1470</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>大洋</t>
+          <t>大統新創</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>357.3250778105711</v>
+        <v>382.6570718815006</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>32.45</v>
+        <v>23.7</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>50.73631496178726</v>
+        <v>50.92365407559508</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>8.566707531370092</v>
+        <v>9.806275768982216</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.6607899626004681</v>
+        <v>0.0747420465119755</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-0.0144298797584978</v>
+        <v>0.096114608249349</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>1342</v>
+        <v>1416</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>八貫</t>
+          <t>廣豐</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>354.7905662744497</v>
+        <v>373.0861512182735</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>101</v>
+        <v>11.45</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,13 +2937,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>46.10594746186332</v>
+        <v>49.76664282805221</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>17.46624571623111</v>
+        <v>15.4819326378806</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.4436552810998709</v>
+        <v>0.5075576072771187</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.1259237989672373</v>
+        <v>-0.0126520572965968</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>1213</v>
+        <v>1309</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>大飲</t>
+          <t>台達化</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>352.4093822999626</v>
+        <v>372.9722255578729</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>7.11</v>
+        <v>13.8</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,13 +2990,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>50.9382346710843</v>
+        <v>52.30168121165394</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>10.20390905301341</v>
+        <v>27.20162786918543</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.1952270638936701</v>
+        <v>0.3390727924063561</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>0.0675868600836383</v>
+        <v>0.0022935548433112</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>1541</v>
+        <v>1233</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>錩泰</t>
+          <t>天仁</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>352.1249085842345</v>
+        <v>368.6379822865925</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>0</v>
+        <v>28.1</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,13 +3043,13 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>30.33335353408724</v>
+        <v>48.27071856087006</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>24.70963790257426</v>
+        <v>11.9693411348231</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0</v>
+        <v>0.8735184449598299</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-1.047930056860007</v>
+        <v>0.011318560176068</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>1215</v>
+        <v>1341</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>卜蜂</t>
+          <t>富林-KY</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>344.472696817404</v>
+        <v>364.8107824047813</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>105.5</v>
+        <v>60</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>41.22010902398039</v>
+        <v>52.16489368283852</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>14.01687633750458</v>
+        <v>10.57232561535845</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>1.67872921694417</v>
+        <v>0.3884383752219517</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-0.3796153909186722</v>
+        <v>1.714778827357518</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>1446</v>
+        <v>1455</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>宏和</t>
+          <t>集盛</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>339.5640837061327</v>
+        <v>360.2971470674685</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>13.6</v>
+        <v>9.68</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,16 +3149,16 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>48.48313166392384</v>
+        <v>46.58871901396223</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>26.1978905740397</v>
+        <v>24.97273180932224</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.3359423949778098</v>
+        <v>0.2162454325099041</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>0.0650936252673958</v>
+        <v>-0.0370862846248416</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>1506</v>
+        <v>1321</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>正道</t>
+          <t>大洋</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>338.2192905484421</v>
+        <v>357.3250778105711</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>9.640000000000001</v>
+        <v>32.45</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>28.35692069100982</v>
+        <v>50.73631469167056</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>27.44815144559506</v>
+        <v>8.566707783910287</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>1.653008422598548</v>
+        <v>0.6607899626004681</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>-0.0139874692320794</v>
+        <v>-0.0144298795963248</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>1110</v>
+        <v>1213</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>東泥</t>
+          <t>大飲</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>333.0183763969389</v>
+        <v>352.4093822999625</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>14.75</v>
+        <v>7.11</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>24.76761647913558</v>
+        <v>50.93823418234832</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>24.94656406823395</v>
+        <v>10.20390864595953</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>3.092441738586137</v>
+        <v>0.1952270638936701</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-0.1118197576063357</v>
+        <v>0.0675868625162675</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>1442</v>
+        <v>1541</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>名軒</t>
+          <t>錩泰</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>331.4637963577783</v>
+        <v>352.1249085842346</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>27.7</v>
+        <v>0</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>32.41645756337766</v>
+        <v>30.33335353128142</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>19.27713957881641</v>
+        <v>24.70963796382662</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.951770542148195</v>
+        <v>0</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-0.2440892928700473</v>
+        <v>-1.047930056869548</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>1402</v>
+        <v>1515</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>遠東新</t>
+          <t>力山</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>323.2765282952909</v>
+        <v>347.2620223312364</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>28.15</v>
+        <v>29.45</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,16 +3361,16 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>49.42826944596607</v>
+        <v>42.42273709710385</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>13.55143725184395</v>
+        <v>9.03585733126558</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.5309790583631036</v>
+        <v>0.3483373997759351</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>-0.08575009693346471</v>
+        <v>-0.0293021760513786</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>1316</v>
+        <v>1215</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>上曜</t>
+          <t>卜蜂</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>321.3485930956717</v>
+        <v>344.4726968174038</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>10.45</v>
+        <v>105.5</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>44.62162332391167</v>
+        <v>41.22010919289527</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>21.31044173490033</v>
+        <v>14.01687637347819</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.5345146938859737</v>
+        <v>1.67872921694417</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-0.0544585819443753</v>
+        <v>-0.3796153910140771</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>1454</v>
+        <v>1446</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>台富</t>
+          <t>宏和</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>320.913672700196</v>
+        <v>339.5640837061327</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>12.3</v>
+        <v>13.6</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>44.31603997038669</v>
+        <v>48.48313166392384</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>22.81993487080907</v>
+        <v>26.19789054212075</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.4719151337708807</v>
+        <v>0.3359423949778098</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,7 +3485,7 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.0012891736037906</v>
+        <v>0.0650936252673958</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
@@ -3495,21 +3495,21 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>1340</v>
+        <v>1506</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>勝悅-KY</t>
+          <t>正道</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>312.7298085177963</v>
+        <v>338.2192905484421</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>5.21</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>50.73108409385419</v>
+        <v>28.35692069100982</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>12.38310156174062</v>
+        <v>27.44815137541359</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.7146941047175062</v>
+        <v>1.653008422598548</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>0.0077391385812424</v>
+        <v>-0.0139874692416193</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>1438</v>
+        <v>1524</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>三地開發</t>
+          <t>耿鼎</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>310.7217290179134</v>
+        <v>337.5014318014976</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>21.5</v>
+        <v>26</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>43.16358179864906</v>
+        <v>38.6317903313488</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>10.65137079891721</v>
+        <v>27.71108258040195</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.8809447083253089</v>
+        <v>0.6761643598881846</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-0.016946959160506</v>
+        <v>-0.0023915764681421</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>1451</v>
+        <v>1529</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>年興</t>
+          <t>樂事綠能</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>310.427635276651</v>
+        <v>337.3024659744194</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>17.1</v>
+        <v>15.45</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>43.29169784449622</v>
+        <v>39.62140688979945</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>18.63885051817316</v>
+        <v>32.55773089204103</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.911360284080754</v>
+        <v>0.5852551952054829</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.0005311493401646</v>
+        <v>0.07935765030684699</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>1210</v>
+        <v>1527</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>大成</t>
+          <t>鑽全</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>307.9902878713745</v>
+        <v>334.2416530707876</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>51.9</v>
+        <v>32.65</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>43.14906613867591</v>
+        <v>50.76748373407746</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>23.50223981769356</v>
+        <v>8.232681164246451</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.5120523351121652</v>
+        <v>0.7607929230308067</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.1264880515523524</v>
+        <v>0.0384647188495408</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>1229</v>
+        <v>1110</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>聯華</t>
+          <t>東泥</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>302.7866031928216</v>
+        <v>333.0183763969388</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>40.1</v>
+        <v>14.75</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>39.89126305045076</v>
+        <v>24.76761666148377</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>16.13051191384759</v>
+        <v>24.9465641163318</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.7020971486000142</v>
+        <v>3.092441738586137</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-0.1374133380498037</v>
+        <v>-0.1118197576540327</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>1504</v>
+        <v>1442</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>東元</t>
+          <t>名軒</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>302.1183274563289</v>
+        <v>331.4637963577784</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>68.5</v>
+        <v>27.7</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,16 +3785,16 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>43.23004484020854</v>
+        <v>32.41645748888907</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>15.93433187584116</v>
+        <v>19.27713960663537</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.7089900705847003</v>
+        <v>0.951770542148195</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-0.3721517106689305</v>
+        <v>-0.2440892927937312</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>1439</v>
+        <v>1229</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>雋揚</t>
+          <t>聯華</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>298.2757444868896</v>
+        <v>322.7866031928216</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>28.15</v>
+        <v>40.1</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,16 +3838,16 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>44.43546677071284</v>
+        <v>39.89126307860599</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>18.87600785482388</v>
+        <v>16.13051192245653</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.1499276599040962</v>
+        <v>0.7020971486000142</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-0.1577845764330976</v>
+        <v>-0.1374133380784252</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>1103</v>
+        <v>1504</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>嘉泥</t>
+          <t>東元</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>297.8901220404101</v>
+        <v>322.1183274563289</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>13.05</v>
+        <v>68.5</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,16 +3891,16 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>44.63866013608353</v>
+        <v>43.23004439744802</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>20.77728968770611</v>
+        <v>15.93433186530655</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.502963476140964</v>
+        <v>0.7089900705847003</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>3.172229322546266e-05</v>
+        <v>-0.3721517096958779</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>1519</v>
+        <v>1316</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>華城</t>
+          <t>上曜</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>292.9792414255553</v>
+        <v>321.3485930956717</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>699</v>
+        <v>10.45</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>44.12876808433585</v>
+        <v>44.62162333988528</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>11.31046957316533</v>
+        <v>21.31044172031665</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.4262569204174543</v>
+        <v>0.5345146938859737</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-2.325496127868256</v>
+        <v>-0.0544585819252956</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>1476</v>
+        <v>1454</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>儒鴻</t>
+          <t>台富</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>292.2727637231952</v>
+        <v>320.9136727001994</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>276.5</v>
+        <v>12.3</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>27.60065121982356</v>
+        <v>44.31603431326939</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>39.59134511643112</v>
+        <v>22.81993488272189</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>1.101667727907232</v>
+        <v>0.4719151337708807</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-0.7220463981309511</v>
+        <v>0.0012891737087281</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>1464</v>
+        <v>1438</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>得力</t>
+          <t>三地開發</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>290.5563946990527</v>
+        <v>310.7217290179134</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>9.970000000000001</v>
+        <v>21.5</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,16 +4050,16 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>39.69797746935376</v>
+        <v>43.16358179864906</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>22.8473379841549</v>
+        <v>10.65137082042527</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.4376298873520786</v>
+        <v>0.8809447083253089</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.0090585001910742</v>
+        <v>-0.0169469591795851</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>1423</v>
+        <v>1451</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>利華</t>
+          <t>年興</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>277.540568178952</v>
+        <v>310.427635276651</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>34.55</v>
+        <v>17.1</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>51.21739120138025</v>
+        <v>43.29169737585897</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>11.48208642132092</v>
+        <v>18.63885063998946</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>1.508667725671662</v>
+        <v>0.911360284080754</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.6964450159835803</v>
+        <v>0.0005311494069418</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>1537</v>
+        <v>1210</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>廣隆</t>
+          <t>大成</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>265.5906114352421</v>
+        <v>307.9902878713745</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>115</v>
+        <v>51.9</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>36.72531310746088</v>
+        <v>43.14906620416949</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>37.98356618088739</v>
+        <v>23.50223984498413</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.7091782403611994</v>
+        <v>0.5120523351121652</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.3264349114988771</v>
+        <v>0.1264880515905116</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>1536</v>
+        <v>1439</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>和大</t>
+          <t>雋揚</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>264.66307813358</v>
+        <v>298.2757444868896</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>47</v>
+        <v>28.15</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>42.71665606363739</v>
+        <v>44.43546668014309</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>9.1406628880471</v>
+        <v>18.87600789052682</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.918806715129435</v>
+        <v>0.1499276599040962</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-0.0378001691136893</v>
+        <v>-0.1577845763663179</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>1477</v>
+        <v>1103</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>聚陽</t>
+          <t>嘉泥</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>262.6367410460276</v>
+        <v>297.8901220404101</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>191</v>
+        <v>13.05</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>37.2977523831274</v>
+        <v>44.63866019244454</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>27.1329773161571</v>
+        <v>20.77728971900297</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.6178356628006788</v>
+        <v>0.502963476140964</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>0.3779994397907762</v>
+        <v>3.172226460564781e-05</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>1216</v>
+        <v>1440</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>統一</t>
+          <t>南紡</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>260.3570762676172</v>
+        <v>293.5820046826983</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>74.5</v>
+        <v>13.5</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>43.20257751603384</v>
+        <v>51.56782478579483</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>8.542082432009572</v>
+        <v>12.99633619565235</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.5435439067548555</v>
+        <v>1.603768348902477</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-0.0541424029477733</v>
+        <v>-0.0309995603711438</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>1319</v>
+        <v>1519</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>東陽</t>
+          <t>華城</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>256.7174706498207</v>
+        <v>292.9792414255554</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>78.90000000000001</v>
+        <v>699</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>45.35370200179072</v>
+        <v>44.12876807303724</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>16.77278611172733</v>
+        <v>11.31046960697478</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.4670247023880471</v>
+        <v>0.4262569204174543</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,7 +4386,7 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-0.2187264450002918</v>
+        <v>-2.325496129776147</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
@@ -4396,21 +4396,21 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>1460</v>
+        <v>1476</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>宏遠</t>
+          <t>儒鴻</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>255.2791340115592</v>
+        <v>292.2727637231952</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>6.25</v>
+        <v>276.5</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>31.90709045651516</v>
+        <v>27.60065125312337</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>22.61088599208442</v>
+        <v>39.5913450503996</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>1.267694664083302</v>
+        <v>1.101667727907232</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-0.010936478126146</v>
+        <v>-0.7220464001343458</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>1414</v>
+        <v>1464</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>東和</t>
+          <t>得力</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>255.2454065857506</v>
+        <v>290.5563946990527</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>17.45</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>40.38847236431168</v>
+        <v>39.69797755024023</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>32.06027475981303</v>
+        <v>22.84733803930289</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.6225557950428553</v>
+        <v>0.4376298873520786</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-0.0039314139904763</v>
+        <v>0.0090585002101527</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>1419</v>
+        <v>1522</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>新紡</t>
+          <t>堤維西</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>251.6014864706753</v>
+        <v>284.5936052404758</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>66</v>
+        <v>26.65</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,16 +4527,16 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>48.37591115172293</v>
+        <v>48.14675888224799</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>12.05625699120556</v>
+        <v>22.71983742039029</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.2763589828495598</v>
+        <v>0.5794892233667036</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-0.1251747436752714</v>
+        <v>0.1215759977745007</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>1410</v>
+        <v>1423</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>南染</t>
+          <t>利華</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>251.4946154716993</v>
+        <v>277.540568178952</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>24</v>
+        <v>34.55</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,16 +4580,16 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>39.6541399921754</v>
+        <v>51.21739120138025</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>7.558030943464066</v>
+        <v>11.48208650327126</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>2.986749443468509</v>
+        <v>1.508667725671662</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.0146174883040368</v>
+        <v>0.6964450159931144</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>1455</v>
+        <v>1537</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>集盛</t>
+          <t>廣隆</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>250.2971470674686</v>
+        <v>265.5906114352421</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>9.68</v>
+        <v>115</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,16 +4633,16 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>46.58871907264504</v>
+        <v>36.72531338978541</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>24.97273179851795</v>
+        <v>37.98356625873164</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.2162454325099041</v>
+        <v>0.7091782403611994</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-0.0370862846458291</v>
+        <v>0.3264349114034752</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>1452</v>
+        <v>1536</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>宏益</t>
+          <t>和大</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>247.4306371673673</v>
+        <v>264.66307813358</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>10.8</v>
+        <v>47</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,16 +4686,16 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>33.06635872946663</v>
+        <v>42.71665610596107</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>23.33689453732472</v>
+        <v>9.140662847124412</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.4179182929817769</v>
+        <v>0.918806715129435</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-0.0355151840551978</v>
+        <v>-0.0378001686748628</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>1515</v>
+        <v>1305</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>力山</t>
+          <t>華夏</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>247.2620223312364</v>
+        <v>264.2101438565873</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>29.45</v>
+        <v>12.1</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,16 +4739,16 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>42.42273709710385</v>
+        <v>50.21515309932448</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>9.035857336157347</v>
+        <v>12.34245574662815</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.3483373997759351</v>
+        <v>0.4095651925805789</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>-0.0293021760036783</v>
+        <v>-0.012616557779775</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>1514</v>
+        <v>1319</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>亞力</t>
+          <t>東陽</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>242.4316965804152</v>
+        <v>256.7174706498207</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>102</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,16 +4792,16 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>49.16387779844552</v>
+        <v>45.35370197292813</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>14.44930210431179</v>
+        <v>16.77278618428673</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>1.351277911539894</v>
+        <v>0.4670247023880471</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>0.3594726389711314</v>
+        <v>-0.2187264450002918</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>1218</v>
+        <v>1460</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>泰山</t>
+          <t>宏遠</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>237.1585734727716</v>
+        <v>255.2791340115592</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>14.4</v>
+        <v>6.25</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>48.71433742666982</v>
+        <v>31.90709045651516</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>5.930345740989829</v>
+        <v>22.61088599681586</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.436274081950618</v>
+        <v>1.267694664083302</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>0.0415502904018147</v>
+        <v>-0.010936478126146</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>1467</v>
+        <v>1414</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>南緯</t>
+          <t>東和</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>235.4608223591782</v>
+        <v>255.2454065857505</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>8.050000000000001</v>
+        <v>17.45</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,16 +4898,16 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>42.16577189759692</v>
+        <v>40.38847242648038</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>10.29497630506662</v>
+        <v>32.06027482614487</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.168613957688645</v>
+        <v>0.6225557950428553</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>0.0310783092113105</v>
+        <v>-0.0039314140558742</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>1517</v>
+        <v>1419</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>利奇</t>
+          <t>新紡</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>227.803280656224</v>
+        <v>251.6014864706753</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>10.3</v>
+        <v>66</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>34.03165138475849</v>
+        <v>48.3759111283575</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>24.15595544987253</v>
+        <v>12.05625700059126</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.2697946046931946</v>
+        <v>0.2763589828495598</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-0.0216342540834645</v>
+        <v>-0.1251747436752714</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>1524</v>
+        <v>1410</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>耿鼎</t>
+          <t>南染</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>227.5014318014976</v>
+        <v>251.4946154716993</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>38.63179034885961</v>
+        <v>39.65414004088515</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>27.71108266778377</v>
+        <v>7.5580309168634</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.6761643598881846</v>
+        <v>2.986749443468509</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-0.0023915765540006</v>
+        <v>0.0146174883231166</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>1201</v>
+        <v>1452</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>味全</t>
+          <t>宏益</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>225.5394686893939</v>
+        <v>247.4306371673675</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>11.6</v>
+        <v>10.8</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>32.59704695175276</v>
+        <v>33.06635877516952</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>29.78140783002045</v>
+        <v>23.3368946476919</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.9539468689393882</v>
+        <v>0.4179182929817769</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-0.047824114445471</v>
+        <v>-0.0355151840742774</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>1232</v>
+        <v>1218</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>大統益</t>
+          <t>泰山</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>224.7163469600592</v>
+        <v>237.1585734727716</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>154.5</v>
+        <v>14.4</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>46.59781338320271</v>
+        <v>48.71433749644433</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>14.55126454884244</v>
+        <v>5.930345808802407</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.5180395055277867</v>
+        <v>0.436274081950618</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-0.2415261606212805</v>
+        <v>0.0415502903731948</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>1453</v>
+        <v>1444</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>大將</t>
+          <t>力麗</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>224.6716848348714</v>
+        <v>236.2889658547867</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>10.9</v>
+        <v>6.86</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,16 +5163,16 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>43.75689479850104</v>
+        <v>43.8817042657624</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>14.52606957164535</v>
+        <v>15.0818304795585</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>1.061136792964763</v>
+        <v>0.5186073575128568</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-0.0083989865653567</v>
+        <v>0.0155526809337908</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>1527</v>
+        <v>1467</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>鑽全</t>
+          <t>南緯</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>224.2416530707877</v>
+        <v>235.4608223591782</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>32.65</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>50.76748530823181</v>
+        <v>42.16577189361502</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>8.23268111131288</v>
+        <v>10.2949763215147</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.7607929230308067</v>
+        <v>0.168613957688645</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>0.0384647186969031</v>
+        <v>0.031078309207495</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>1409</v>
+        <v>1514</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>新纖</t>
+          <t>亞力</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>223.7950026311044</v>
+        <v>232.4316965804152</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>24.3</v>
+        <v>102</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>48.64578570695821</v>
+        <v>49.16387781592628</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>12.18296462007826</v>
+        <v>14.44930207695184</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.2249250096795675</v>
+        <v>1.351277911539894</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>-0.0838127958642661</v>
+        <v>0.3594726392573232</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>1256</v>
+        <v>1517</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>鮮活果汁-KY</t>
+          <t>利奇</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>222.7467763968065</v>
+        <v>227.803280656224</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>166.5</v>
+        <v>10.3</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>33.17979772439234</v>
+        <v>34.03165126832047</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>8.769809627978258</v>
+        <v>24.15595550586509</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.7535309221377681</v>
+        <v>0.2697946046931946</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-0.4561794849406828</v>
+        <v>-0.0216342540739243</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>1529</v>
+        <v>1201</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>樂事綠能</t>
+          <t>味全</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>222.3024659744196</v>
+        <v>225.5394686893939</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>15.45</v>
+        <v>11.6</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>39.6214069373902</v>
+        <v>32.59704691572874</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>32.5577310036352</v>
+        <v>29.78140831715586</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.5852551952054829</v>
+        <v>0.9539468689393882</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,7 +5393,7 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>0.07935765025914809</v>
+        <v>-0.0478241144263929</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
@@ -5403,21 +5403,21 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>1220</v>
+        <v>1232</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>台榮</t>
+          <t>大統益</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>220.5989157019269</v>
+        <v>224.7163469600592</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>10.75</v>
+        <v>154.5</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>40.61848549929505</v>
+        <v>46.59781347622856</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>17.86580192590779</v>
+        <v>14.55126456953445</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.4362253128082805</v>
+        <v>0.5180395055277867</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>0.0126355083790777</v>
+        <v>-0.24152616081207</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>1435</v>
+        <v>1453</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>中福</t>
+          <t>大將</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>220.2432696812492</v>
+        <v>224.6716848348714</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>22.25</v>
+        <v>10.9</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>50.912004432837</v>
+        <v>43.75689453703884</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>8.920657531897053</v>
+        <v>14.52606952527272</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.603459583538285</v>
+        <v>1.061136792964763</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>0.3059918061064576</v>
+        <v>-0.008398986498580299</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>1440</v>
+        <v>1409</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>南紡</t>
+          <t>新纖</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>218.5820046826983</v>
+        <v>223.7950026311044</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>13.5</v>
+        <v>24.3</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,16 +5534,16 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>51.56782482705388</v>
+        <v>48.64578567582122</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>12.99633617362501</v>
+        <v>12.18296457283881</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>1.603768348902477</v>
+        <v>0.2249250096795675</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-0.0309995603902223</v>
+        <v>-0.0838127958451875</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>1444</v>
+        <v>1256</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>力麗</t>
+          <t>鮮活果汁-KY</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>216.2889658547867</v>
+        <v>222.7467763968065</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>6.86</v>
+        <v>166.5</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>43.88170424188564</v>
+        <v>33.17979778344731</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>15.08183040220678</v>
+        <v>8.769809614254433</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.5186073575128568</v>
+        <v>0.7535309221377681</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>0.0155526809414227</v>
+        <v>-0.4561794849406828</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>1109</v>
+        <v>1220</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>信大</t>
+          <t>台榮</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>215.4429671167574</v>
+        <v>220.5989157019269</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>13.3</v>
+        <v>10.75</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>34.86046125500562</v>
+        <v>40.61848543601389</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>32.47825080745528</v>
+        <v>17.86580193502385</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.7728841266485443</v>
+        <v>0.4362253128082805</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>0.0029119068664144</v>
+        <v>0.0126355083886178</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>1582</v>
+        <v>1435</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>信錦</t>
+          <t>中福</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>211.1869988943316</v>
+        <v>220.2432696812492</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>70</v>
+        <v>22.25</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>39.54037476884975</v>
+        <v>50.91200453318152</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>23.16157984223712</v>
+        <v>8.920657514251682</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.6938625427939001</v>
+        <v>0.603459583538285</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-0.0581086237141195</v>
+        <v>0.3059918048370221</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>1443</v>
+        <v>1109</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>立益</t>
+          <t>信大</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>210.8729195606529</v>
+        <v>215.4429671167574</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>23.05</v>
+        <v>13.3</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>45.25963939978308</v>
+        <v>34.86046143660859</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>5.119036104835292</v>
+        <v>32.47825081832897</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.8622069614414106</v>
+        <v>0.7728841266485443</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-0.0033726783989406</v>
+        <v>0.0029119068377951</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>1525</v>
+        <v>1227</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>江申</t>
+          <t>佳格</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>194.21796190161</v>
+        <v>211.8394895216232</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>64.40000000000001</v>
+        <v>28.15</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,16 +5799,16 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>51.18018451166769</v>
+        <v>41.08444409117836</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>21.54249086173267</v>
+        <v>10.97575315166562</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>1.504848647200643</v>
+        <v>0.8187801994017417</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-1.184543157833784</v>
+        <v>0.0050552602008418</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>1227</v>
+        <v>1582</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>佳格</t>
+          <t>信錦</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>191.8394895216232</v>
+        <v>211.1869988943315</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>28.15</v>
+        <v>70</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>41.08444403295702</v>
+        <v>39.5403749382553</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>10.97575316743732</v>
+        <v>23.16157988497739</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.8187801994017417</v>
+        <v>0.6938625427939001</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>0.0050552602294611</v>
+        <v>-0.0581086236187191</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>1539</v>
+        <v>1443</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>巨庭</t>
+          <t>立益</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>181.5227854440416</v>
+        <v>210.8729195606529</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>15.5</v>
+        <v>23.05</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>42.75937492734037</v>
+        <v>45.25963939602129</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>16.36644319302922</v>
+        <v>5.119036127622759</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>1.081609927212568</v>
+        <v>0.8622069614414106</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>0.0069930216238974</v>
+        <v>-0.0033726784275606</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>1203</v>
+        <v>1219</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>味王</t>
+          <t>福壽</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>179.1261910377823</v>
+        <v>201.2880144375582</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>43.3</v>
+        <v>11.45</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,16 +5958,16 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>45.46547029684382</v>
+        <v>50.43547673679654</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>13.1956353681847</v>
+        <v>18.06665914057961</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.5325164438786336</v>
+        <v>0.9288049767465556</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-0.0114865284804126</v>
+        <v>0.0076157054992209</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>1503</v>
+        <v>1525</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>士電</t>
+          <t>江申</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>177.8432355317166</v>
+        <v>194.2179619016075</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>196</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>43.30531216394055</v>
+        <v>51.18018452391785</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>10.00399059286265</v>
+        <v>21.54249097412362</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.425144086768141</v>
+        <v>1.504848647200643</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.5422818146386039</v>
+        <v>-1.184543157910109</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>1522</v>
+        <v>1539</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>堤維西</t>
+          <t>巨庭</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>174.5936052404757</v>
+        <v>181.5227854440416</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>26.65</v>
+        <v>15.5</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,16 +6064,16 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>48.14675892641744</v>
+        <v>42.75937490525939</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>22.71983742225776</v>
+        <v>16.36644319748243</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.5794892233667036</v>
+        <v>1.081609927212568</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>0.1215759975932456</v>
+        <v>0.0069930216143574</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>1540</v>
+        <v>1203</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>喬福</t>
+          <t>味王</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>174.4332721177513</v>
+        <v>179.1261910377823</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>19.5</v>
+        <v>43.3</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>48.39438030642329</v>
+        <v>45.46547026813975</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>12.54145279000107</v>
+        <v>13.19563537735114</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.5535224586928081</v>
+        <v>0.5325164438786336</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>0.0512900792658932</v>
+        <v>-0.0114865284899529</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>1472</v>
+        <v>1503</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>三洋實業</t>
+          <t>士電</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>173.7987715527221</v>
+        <v>177.8432355317165</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>88</v>
+        <v>196</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>52.77989777839887</v>
+        <v>43.30531210020706</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>9.167122633370742</v>
+        <v>10.00399064412504</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.4798771552722107</v>
+        <v>0.425144086768141</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>2.690341496353078</v>
+        <v>-0.54228181406623</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>1325</v>
+        <v>1540</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>恆大</t>
+          <t>喬福</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>173.0517324139478</v>
+        <v>174.4332721177512</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>25.7</v>
+        <v>19.5</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>47.78896384028182</v>
+        <v>48.39438040279474</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>15.68770200341372</v>
+        <v>12.5414528936279</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>1.138063168865906</v>
+        <v>0.5535224586928081</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>0.0102298855002794</v>
+        <v>0.0512900794089901</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>1538</v>
+        <v>1472</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>正峰</t>
+          <t>三洋實業</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>172.3386763994989</v>
+        <v>173.7987715527221</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>45.75353360973266</v>
+        <v>52.77989777201535</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>11.43605744118501</v>
+        <v>9.1671226089423</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.0001400550416313</v>
+        <v>0.4798771552722107</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-0.3148516972777656</v>
+        <v>2.690341496505717</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>1475</v>
+        <v>1538</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>業旺</t>
+          <t>正峰</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>172.0907985328736</v>
+        <v>172.338676399499</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>26.35</v>
+        <v>0</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>51.91879875190717</v>
+        <v>45.75353411473413</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>19.44384810773671</v>
+        <v>11.43605780234731</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.2236906510034263</v>
+        <v>0.0001400550416313</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>0.0404375592480974</v>
+        <v>-0.3148517024673754</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>1530</v>
+        <v>1475</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>亞崴</t>
+          <t>業旺</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>161.8770216573474</v>
+        <v>172.0907985328736</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>26.7</v>
+        <v>26.35</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>32.86232833379606</v>
+        <v>51.91879873819772</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>19.10831845434487</v>
+        <v>19.44384807920188</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.3016058633221153</v>
+        <v>0.2236906510034263</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-0.1218205302587026</v>
+        <v>0.0404375592194801</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>地球</t>
+          <t>恆大</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>161.3846023104533</v>
+        <v>163.0517324139478</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>10.05</v>
+        <v>25.7</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>49.9028075079507</v>
+        <v>47.78896417967887</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>12.69467954931075</v>
+        <v>15.68770208826056</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>1.087615949355959</v>
+        <v>1.138063168865906</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.0005648757909755</v>
+        <v>0.0102298855288995</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>1512</v>
+        <v>1530</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>瑞利</t>
+          <t>亞崴</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>160.7915541841324</v>
+        <v>161.8770216573484</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>6.18</v>
+        <v>26.7</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>38.80466816066468</v>
+        <v>32.86232829554959</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>9.519760031414132</v>
+        <v>19.10831854223087</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.9554569055577288</v>
+        <v>0.3016058633221153</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,28 +6506,28 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>0.0102867784513679</v>
+        <v>-0.1218205302396243</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>1445</v>
+        <v>1324</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>大宇</t>
+          <t>地球</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>158.1547494433739</v>
+        <v>161.3846023104533</v>
       </c>
       <c r="E115" s="2" t="n">
         <v>10.05</v>
@@ -6541,13 +6541,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>41.02453338968546</v>
+        <v>49.90280746149206</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>10.16589350906592</v>
+        <v>12.69467963153254</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.1011474815970939</v>
+        <v>1.087615949355959</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>0</v>
@@ -6559,31 +6559,31 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-0.0017563048356585</v>
+        <v>-0.0005648757909755</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>1526</v>
+        <v>1512</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>日馳</t>
+          <t>瑞利</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>156.3472657772318</v>
+        <v>160.7915541841325</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>14.7</v>
+        <v>6.18</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,13 +6594,13 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>36.77541195640906</v>
+        <v>38.80466856445916</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>23.03727367864174</v>
+        <v>9.519760066748011</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.1997971702293157</v>
+        <v>0.9554569055577288</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>0</v>
@@ -6612,31 +6612,31 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-0.0115572103528618</v>
+        <v>0.0102867784494589</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>1465</v>
+        <v>1445</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>偉全</t>
+          <t>大宇</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>156.2713990392806</v>
+        <v>158.1547494433739</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>11.6</v>
+        <v>10.05</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,13 +6647,13 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>37.80698424587857</v>
+        <v>41.02453311432241</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>17.25404831647522</v>
+        <v>10.16589349199025</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.09485171628344451</v>
+        <v>0.1011474815970939</v>
       </c>
       <c r="K117" s="2" t="n">
         <v>0</v>
@@ -6665,31 +6665,31 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>-0.0140613970301036</v>
+        <v>-0.0017563047307236</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>1305</v>
+        <v>1526</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>華夏</t>
+          <t>日馳</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>154.2101438565872</v>
+        <v>156.3472657772318</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>12.1</v>
+        <v>14.7</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,13 +6700,13 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>50.2151531133232</v>
+        <v>36.77541197846822</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>12.34245568764647</v>
+        <v>23.0372737273773</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.4095651925805789</v>
+        <v>0.1997971702293157</v>
       </c>
       <c r="K118" s="2" t="n">
         <v>0</v>
@@ -6718,31 +6718,31 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>-0.0126165576843778</v>
+        <v>-0.0115572104005615</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>1533</v>
+        <v>1465</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>車王電</t>
+          <t>偉全</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>154.0283597477357</v>
+        <v>156.2713990392806</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>30.3</v>
+        <v>11.6</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,13 +6753,13 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>39.10305947745956</v>
+        <v>37.80698432934248</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>15.84860760244879</v>
+        <v>17.25404834173696</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.2898815301299903</v>
+        <v>0.09485171628344451</v>
       </c>
       <c r="K119" s="2" t="n">
         <v>0</v>
@@ -6771,7 +6771,7 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>0.0639195305219997</v>
+        <v>-0.014061397039644</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
@@ -6781,21 +6781,21 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>1231</v>
+        <v>1533</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>聯華食</t>
+          <t>車王電</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>150.6907412260265</v>
+        <v>154.0283597477357</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>79.59999999999999</v>
+        <v>30.3</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,13 +6806,13 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>41.33665300540563</v>
+        <v>39.10305944947053</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>10.76942203219696</v>
+        <v>15.84860772938364</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.5036580712732786</v>
+        <v>0.2898815301299903</v>
       </c>
       <c r="K120" s="2" t="n">
         <v>0</v>
@@ -6824,7 +6824,7 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>0.1293157683696939</v>
+        <v>0.0639195305219997</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
@@ -6834,21 +6834,21 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>1413</v>
+        <v>1231</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>宏洲</t>
+          <t>聯華食</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>147.7983562297197</v>
+        <v>150.6907412260265</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>9.19</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,16 +6859,16 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>46.17349656131834</v>
+        <v>41.33665312453917</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>8.802496511616388</v>
+        <v>10.76942217858215</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.3445227478682101</v>
+        <v>0.5036580712732786</v>
       </c>
       <c r="K121" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L121" s="2" t="n">
         <v>0</v>
@@ -6877,7 +6877,7 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>0.0059497130188572</v>
+        <v>0.1293157686558813</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
@@ -6887,21 +6887,21 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>1457</v>
+        <v>1413</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>宜進</t>
+          <t>宏洲</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>143.2164431712959</v>
+        <v>147.7983562297197</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>14.35</v>
+        <v>9.19</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,13 +6912,13 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>47.14649688749172</v>
+        <v>46.1734966564245</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>11.92050068109941</v>
+        <v>8.802496416839771</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>0.5152589055244483</v>
+        <v>0.3445227478682101</v>
       </c>
       <c r="K122" s="2" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>-0.0076900530347278</v>
+        <v>0.0059497130093179</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
@@ -6940,21 +6940,21 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>1225</v>
+        <v>1457</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>福懋油</t>
+          <t>宜進</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>139.7124922656049</v>
+        <v>143.216443171296</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>24.45</v>
+        <v>14.35</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6965,16 +6965,16 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>43.64610475103562</v>
+        <v>47.14649695124344</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>19.23217657285925</v>
+        <v>11.92050054080074</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.1051216414652538</v>
+        <v>0.5152589055244483</v>
       </c>
       <c r="K123" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L123" s="2" t="n">
         <v>0</v>
@@ -6983,31 +6983,31 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>0.0159319402160263</v>
+        <v>-0.0076900530347278</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>1447</v>
+        <v>1225</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>力鵬</t>
+          <t>福懋油</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>135.4576077601543</v>
+        <v>139.7124922656049</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>6.39</v>
+        <v>24.45</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7018,13 +7018,13 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>39.06292271346211</v>
+        <v>43.64610467316226</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>9.452739799952887</v>
+        <v>19.23217670651324</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.7371579717980277</v>
+        <v>0.1051216414652538</v>
       </c>
       <c r="K124" s="2" t="n">
         <v>0</v>
@@ -7036,31 +7036,31 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>-0.0005736163216236</v>
+        <v>0.0159319404163587</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>1468</v>
+        <v>1466</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>昶和</t>
+          <t>聚隆</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
         <v/>
       </c>
       <c r="D125" s="2" t="n">
-        <v>126.973302907767</v>
+        <v>137.164246258769</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>13.2</v>
+        <v>14.75</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
@@ -7071,16 +7071,16 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>50.92732670381618</v>
+        <v>36.18091045899258</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>10.55419103366479</v>
+        <v>9.354981190098441</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>0.7333678287830576</v>
+        <v>0.2862937149337433</v>
       </c>
       <c r="K125" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L125" s="2" t="n">
         <v>0</v>
@@ -7089,31 +7089,31 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>-0.0101972522631299</v>
+        <v>-0.0036221740890226</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>1466</v>
+        <v>1447</v>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>聚隆</t>
+          <t>力鵬</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
         <v/>
       </c>
       <c r="D126" s="2" t="n">
-        <v>117.164246258769</v>
+        <v>135.4576077601543</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>14.75</v>
+        <v>6.39</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -7124,13 +7124,13 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>36.18091056599943</v>
+        <v>39.06292275115396</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>9.354981215979191</v>
+        <v>9.452739815720539</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>0.2862937149337433</v>
+        <v>0.7371579717980277</v>
       </c>
       <c r="K126" s="2" t="n">
         <v>0</v>
@@ -7142,31 +7142,31 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>-0.0036221741271832</v>
+        <v>-0.0005736163216236</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>1436</v>
+        <v>1468</v>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>華友聯</t>
+          <t>昶和</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
         <v/>
       </c>
       <c r="D127" s="2" t="n">
-        <v>110.8101094115274</v>
+        <v>126.973302907767</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>36.15</v>
+        <v>13.2</v>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
@@ -7177,13 +7177,13 @@
         <v>0</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>39.96116760355096</v>
+        <v>50.9273266867197</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>18.30873217286675</v>
+        <v>10.55419107212293</v>
       </c>
       <c r="J127" s="2" t="n">
-        <v>0.5127334465195246</v>
+        <v>0.7333678287830576</v>
       </c>
       <c r="K127" s="2" t="n">
         <v>0</v>
@@ -7195,31 +7195,31 @@
         <v>-1</v>
       </c>
       <c r="N127" s="2" t="n">
-        <v>0.0015208743871629</v>
+        <v>-0.0101972522726693</v>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>1532</v>
+        <v>1436</v>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>勤美</t>
+          <t>華友聯</t>
         </is>
       </c>
       <c r="C128" s="2" t="n">
         <v/>
       </c>
       <c r="D128" s="2" t="n">
-        <v>105.5320997636753</v>
+        <v>110.8101094115274</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>22.3</v>
+        <v>36.15</v>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
@@ -7230,13 +7230,13 @@
         <v>0</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>41.89733788222578</v>
+        <v>39.96116768194389</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>14.10139025006954</v>
+        <v>18.30873215953499</v>
       </c>
       <c r="J128" s="2" t="n">
-        <v>0.9779548285610944</v>
+        <v>0.5127334465195246</v>
       </c>
       <c r="K128" s="2" t="n">
         <v>0</v>
@@ -7248,7 +7248,7 @@
         <v>-1</v>
       </c>
       <c r="N128" s="2" t="n">
-        <v>-0.0484924270313841</v>
+        <v>0.0015208744634838</v>
       </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
@@ -7258,21 +7258,21 @@
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
-        <v>1219</v>
+        <v>1532</v>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>福壽</t>
+          <t>勤美</t>
         </is>
       </c>
       <c r="C129" s="2" t="n">
         <v/>
       </c>
       <c r="D129" s="2" t="n">
-        <v>91.28801443755816</v>
+        <v>105.5320997636753</v>
       </c>
       <c r="E129" s="2" t="n">
-        <v>11.45</v>
+        <v>22.3</v>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
@@ -7283,13 +7283,13 @@
         <v>0</v>
       </c>
       <c r="H129" s="2" t="n">
-        <v>50.43547669079154</v>
+        <v>41.89733815074717</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>18.06665912133473</v>
+        <v>14.10139027183106</v>
       </c>
       <c r="J129" s="2" t="n">
-        <v>0.9288049767465556</v>
+        <v>0.9779548285610944</v>
       </c>
       <c r="K129" s="2" t="n">
         <v>0</v>
@@ -7301,7 +7301,7 @@
         <v>-1</v>
       </c>
       <c r="N129" s="2" t="n">
-        <v>0.0076157055183002</v>
+        <v>-0.0484924271076976</v>
       </c>
       <c r="O129" s="2" t="inlineStr">
         <is>
@@ -7339,7 +7339,7 @@
         <v>49.14989578507964</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>13.93374917535014</v>
+        <v>13.93374916693373</v>
       </c>
       <c r="J130" s="2" t="n">
         <v>0.7975212146144058</v>
@@ -7375,7 +7375,7 @@
         <v/>
       </c>
       <c r="D131" s="2" t="n">
-        <v>88.34879135601554</v>
+        <v>88.34879135601571</v>
       </c>
       <c r="E131" s="2" t="n">
         <v>9.4</v>
@@ -7389,10 +7389,10 @@
         <v>0</v>
       </c>
       <c r="H131" s="2" t="n">
-        <v>42.81461532260967</v>
+        <v>42.81461567884486</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>15.55587070469132</v>
+        <v>15.5558706878708</v>
       </c>
       <c r="J131" s="2" t="n">
         <v>0.5619201813244366</v>
@@ -7407,7 +7407,7 @@
         <v>-1</v>
       </c>
       <c r="N131" s="2" t="n">
-        <v>-0.0082758694820739</v>
+        <v>-0.008275869476349</v>
       </c>
       <c r="O131" s="2" t="inlineStr">
         <is>
@@ -7442,10 +7442,10 @@
         <v>0</v>
       </c>
       <c r="H132" s="2" t="n">
-        <v>51.74505591950721</v>
+        <v>51.74505613837026</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>11.7786326974106</v>
+        <v>11.77863272633815</v>
       </c>
       <c r="J132" s="2" t="n">
         <v>0.6524428229882353</v>
@@ -7495,10 +7495,10 @@
         <v>0</v>
       </c>
       <c r="H133" s="2" t="n">
-        <v>44.53314507754759</v>
+        <v>44.53314503206301</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>12.80569385125761</v>
+        <v>12.80569380572918</v>
       </c>
       <c r="J133" s="2" t="n">
         <v>0.2469258623831483</v>
@@ -7513,7 +7513,7 @@
         <v>-1</v>
       </c>
       <c r="N133" s="2" t="n">
-        <v>-0.0580568853714103</v>
+        <v>-0.0580568853523309</v>
       </c>
       <c r="O133" s="2" t="inlineStr">
         <is>

--- a/output/full_scan/batch_seq1_2026-09-24.xlsx
+++ b/output/full_scan/batch_seq1_2026-09-24.xlsx
@@ -555,7 +555,7 @@
         <v>76.76980525541725</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>31.41680151569321</v>
+        <v>31.4168015702786</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>1.008498413392119</v>
@@ -570,7 +570,7 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>24.49570838820415</v>
+        <v>24.49570838768908</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
@@ -605,10 +605,10 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>79.89106156477303</v>
+        <v>79.89106143081827</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>53.06968872101748</v>
+        <v>53.06968890241327</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>2.741649652972179</v>
@@ -623,7 +623,7 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>1.590931852628519</v>
+        <v>1.590931853720629</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
@@ -658,10 +658,10 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>58.61440123410856</v>
+        <v>58.61440598226877</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>17.18896284450348</v>
+        <v>17.18896536541293</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>1.283795586748832</v>
@@ -676,7 +676,7 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.0340843764825968</v>
+        <v>0.0340843738862658</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
@@ -711,10 +711,10 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>56.55433796133729</v>
+        <v>56.55433808511896</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>40.34462201169195</v>
+        <v>40.34462239767203</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>0.1895911116324685</v>
@@ -729,7 +729,7 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>-0.07519359721979239</v>
+        <v>-0.0751935973454885</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
@@ -764,10 +764,10 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>60.93299628994088</v>
+        <v>60.93299614592757</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>26.89643561385643</v>
+        <v>26.89643566749574</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>0.999049460502734</v>
@@ -782,7 +782,7 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.008277293785017001</v>
+        <v>0.0082772938571382</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>58.09717153367886</v>
+        <v>58.09717154455284</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>23.99712451639491</v>
+        <v>23.99712473988518</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>0.7949632640336151</v>
@@ -835,7 +835,7 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>-1.694069483020671</v>
+        <v>-1.694069483463693</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
@@ -870,10 +870,10 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>75.4911544196669</v>
+        <v>75.49115445273235</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>45.93921653948664</v>
+        <v>45.93921664763305</v>
       </c>
       <c r="J8" s="2" t="n">
         <v>0.3006969482605902</v>
@@ -888,7 +888,7 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.068229957271102</v>
+        <v>0.06822995720925989</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>678.8243237025708</v>
+        <v>678.8243237025711</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>25.45</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>65.72105385539237</v>
+        <v>65.72105379229193</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>37.09592352816865</v>
+        <v>37.09592363131511</v>
       </c>
       <c r="J9" s="2" t="n">
         <v>0.7737003345632983</v>
@@ -941,7 +941,7 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.4556074238322736</v>
+        <v>0.4556074240692371</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
@@ -976,10 +976,10 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>68.29302356023521</v>
+        <v>68.29302357750073</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>48.45375435943801</v>
+        <v>48.45375427393484</v>
       </c>
       <c r="J10" s="2" t="n">
         <v>0.1306458913668709</v>
@@ -1029,10 +1029,10 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>58.52601509604765</v>
+        <v>58.52601513452927</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>31.75787821900792</v>
+        <v>31.75787830596096</v>
       </c>
       <c r="J11" s="2" t="n">
         <v>0.6525081178999347</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>60.71553075306982</v>
+        <v>60.71553072717938</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>34.27801528573151</v>
+        <v>34.27801534311887</v>
       </c>
       <c r="J12" s="2" t="n">
         <v>0.4865206968699114</v>
@@ -1100,7 +1100,7 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>-0.3412781365943997</v>
+        <v>-0.341278136417837</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -1135,10 +1135,10 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>60.28988304091983</v>
+        <v>60.28988319413902</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>18.1143949937001</v>
+        <v>18.11439463217432</v>
       </c>
       <c r="J13" s="2" t="n">
         <v>1.438336874983999</v>
@@ -1153,7 +1153,7 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.0821446360632689</v>
+        <v>0.0821446363620538</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>617.5477520375175</v>
+        <v>617.5477520375176</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>12.5</v>
@@ -1188,10 +1188,10 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>53.53620395911947</v>
+        <v>53.53620403183438</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>21.43000304873751</v>
+        <v>21.43000327057417</v>
       </c>
       <c r="J14" s="2" t="n">
         <v>0.7923255890524106</v>
@@ -1206,7 +1206,7 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.001400774055535</v>
+        <v>0.001400773993717</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>52.0899266163139</v>
+        <v>52.08992669373536</v>
       </c>
       <c r="I15" s="2" t="n">
         <v>10.26933187518033</v>
@@ -1294,10 +1294,10 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>51.63017679584309</v>
+        <v>51.63017684017526</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>28.26579655622348</v>
+        <v>28.26579695102428</v>
       </c>
       <c r="J16" s="2" t="n">
         <v>0.5053244878320772</v>
@@ -1312,7 +1312,7 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>-0.6345949734404042</v>
+        <v>-0.6345949737597965</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1347,10 +1347,10 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>71.14387127086208</v>
+        <v>71.14387143480535</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>36.11969021148665</v>
+        <v>36.11969027829939</v>
       </c>
       <c r="J17" s="2" t="n">
         <v>0.4134116033172695</v>
@@ -1365,7 +1365,7 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>0.1645810012960185</v>
+        <v>0.1645810011723649</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>53.23083443494485</v>
+        <v>53.23083455005789</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>22.95163970565744</v>
+        <v>22.9516400415005</v>
       </c>
       <c r="J18" s="2" t="n">
         <v>0.5460843204995706</v>
@@ -1418,7 +1418,7 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>-0.3531246927553171</v>
+        <v>-0.3531246933425762</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1453,10 +1453,10 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>51.93921032324754</v>
+        <v>51.93921035606791</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>23.12381048549101</v>
+        <v>23.12381053684191</v>
       </c>
       <c r="J19" s="2" t="n">
         <v>0.7842704691768611</v>
@@ -1471,7 +1471,7 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.002710323799178</v>
+        <v>0.0027103237888756</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
@@ -1506,10 +1506,10 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>44.40915745656954</v>
+        <v>44.40915747510478</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>15.14464571268223</v>
+        <v>15.14464573862796</v>
       </c>
       <c r="J20" s="2" t="n">
         <v>0.2270158080671501</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>60.70055981570912</v>
+        <v>60.70055988039058</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>41.10032606681857</v>
+        <v>41.10032647486013</v>
       </c>
       <c r="J21" s="2" t="n">
         <v>1.013911217114202</v>
@@ -1577,7 +1577,7 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0.07525803329222081</v>
+        <v>0.0752580332551296</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1612,10 +1612,10 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>54.08287234028921</v>
+        <v>54.08287236493935</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>15.87081660312091</v>
+        <v>15.87081657321302</v>
       </c>
       <c r="J22" s="2" t="n">
         <v>0.407092049387347</v>
@@ -1630,7 +1630,7 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>-0.0417863745310384</v>
+        <v>-0.0417863745413435</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1665,10 +1665,10 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>56.79220562504735</v>
+        <v>56.79220558377262</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>15.71171700071069</v>
+        <v>15.71171701028789</v>
       </c>
       <c r="J23" s="2" t="n">
         <v>1.105566558177927</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>53.48114731366788</v>
+        <v>53.48114735305222</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>27.67049543656308</v>
+        <v>27.67049570260034</v>
       </c>
       <c r="J24" s="2" t="n">
         <v>0.6537112824940586</v>
@@ -1736,7 +1736,7 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>-0.0210725773042343</v>
+        <v>-0.0210725773454489</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -1771,10 +1771,10 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>55.48243554290518</v>
+        <v>55.48243570517651</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>28.35361327067837</v>
+        <v>28.35361368408314</v>
       </c>
       <c r="J25" s="2" t="n">
         <v>0.6913980111746824</v>
@@ -1789,7 +1789,7 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.0247344407166157</v>
+        <v>0.0247344406259506</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>496.2549857292478</v>
+        <v>496.2549857292479</v>
       </c>
       <c r="E26" s="2" t="n">
         <v>30.9</v>
@@ -1824,10 +1824,10 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>58.45887265302812</v>
+        <v>58.45887262375558</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>18.71366384816152</v>
+        <v>18.71366386828052</v>
       </c>
       <c r="J26" s="2" t="n">
         <v>0.7051406157625537</v>
@@ -1842,7 +1842,7 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>0.2561221695572497</v>
+        <v>0.2561221695984589</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>48.82640971135586</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>12.27444449253986</v>
+        <v>12.2744445123444</v>
       </c>
       <c r="J27" s="2" t="n">
         <v>1.531400252959722</v>
@@ -1930,10 +1930,10 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>49.68909414829141</v>
+        <v>49.6890941959791</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>21.08901584924069</v>
+        <v>21.08901632706459</v>
       </c>
       <c r="J28" s="2" t="n">
         <v>0.7878205253041712</v>
@@ -1948,7 +1948,7 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.0164448750207527</v>
+        <v>0.0164448750413579</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>42.50966776336448</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>28.89237807896638</v>
+        <v>28.89237810026683</v>
       </c>
       <c r="J29" s="2" t="n">
         <v>2.508345645706944</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>39.64992315276202</v>
+        <v>39.6499231005707</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>20.7979220757806</v>
+        <v>20.79792211131302</v>
       </c>
       <c r="J30" s="2" t="n">
         <v>0.5862350659408259</v>
@@ -2054,7 +2054,7 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.0154544951585713</v>
+        <v>0.0154544952203942</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
@@ -2089,10 +2089,10 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>46.10594759896849</v>
+        <v>46.10594747465212</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>17.46624579589394</v>
+        <v>17.46624585831511</v>
       </c>
       <c r="J31" s="2" t="n">
         <v>0.4436552810998709</v>
@@ -2107,7 +2107,7 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.1259237989099998</v>
+        <v>0.1259237993221172</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>462.555327862438</v>
+        <v>462.5553278624379</v>
       </c>
       <c r="E32" s="2" t="n">
         <v>14.75</v>
@@ -2142,10 +2142,10 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>53.58774456843417</v>
+        <v>53.5877446750235</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>34.09691411825446</v>
+        <v>34.09691412721011</v>
       </c>
       <c r="J32" s="2" t="n">
         <v>1.795983580426009</v>
@@ -2160,7 +2160,7 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.09347685506407941</v>
+        <v>0.0934768550125628</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         <v>44.18436452915455</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>13.92977534151037</v>
+        <v>13.92977540369517</v>
       </c>
       <c r="J33" s="2" t="n">
         <v>1.053801751042616</v>
@@ -2213,7 +2213,7 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>-0.0102843300146885</v>
+        <v>-0.0102843299819899</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>36.43831637129214</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>21.99582902388497</v>
+        <v>21.99582910455362</v>
       </c>
       <c r="J34" s="2" t="n">
         <v>2.528985684292139</v>
@@ -2301,10 +2301,10 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>37.29775235181029</v>
+        <v>37.29775226429642</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>27.13297728318202</v>
+        <v>27.13297719712186</v>
       </c>
       <c r="J35" s="2" t="n">
         <v>0.6178356628006788</v>
@@ -2319,7 +2319,7 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>0.3779994403631903</v>
+        <v>0.3779994407752971</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>450.357076267617</v>
+        <v>450.3570762676169</v>
       </c>
       <c r="E36" s="2" t="n">
         <v>74.5</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>43.20257755502521</v>
+        <v>43.20257747606914</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>8.542082484448462</v>
+        <v>8.542082375698199</v>
       </c>
       <c r="J36" s="2" t="n">
         <v>0.5435439067548555</v>
@@ -2372,7 +2372,7 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-0.0541424029096032</v>
+        <v>-0.0541424027859738</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
@@ -2407,10 +2407,10 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>49.42826946386565</v>
+        <v>49.42826941589242</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>13.55143727436524</v>
+        <v>13.55143722092805</v>
       </c>
       <c r="J37" s="2" t="n">
         <v>0.5977734942476089</v>
@@ -2425,7 +2425,7 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>-0.085750096914386</v>
+        <v>-0.0857500968731737</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
@@ -2460,10 +2460,10 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>54.70469457080497</v>
+        <v>54.70469487406808</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>22.30187226707582</v>
+        <v>22.3018726441397</v>
       </c>
       <c r="J38" s="2" t="n">
         <v>0.5316251204259922</v>
@@ -2478,7 +2478,7 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.0140783796872897</v>
+        <v>0.0140783795203816</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>44.72683621650541</v>
+        <v>44.72683610069753</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>18.44940284513235</v>
+        <v>18.44940280019104</v>
       </c>
       <c r="J39" s="2" t="n">
         <v>0.7415643761119077</v>
@@ -2531,7 +2531,7 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>-0.112225682320523</v>
+        <v>-0.1122256822793139</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
@@ -2566,10 +2566,10 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>57.08322859267743</v>
+        <v>57.08322822726369</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>17.18057315787357</v>
+        <v>17.18057368936899</v>
       </c>
       <c r="J40" s="2" t="n">
         <v>1.201204532330209</v>
@@ -2584,7 +2584,7 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.0574064350294469</v>
+        <v>0.0574064352045982</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
@@ -2619,10 +2619,10 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>50.7310841260519</v>
+        <v>50.7310841029356</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>12.38310166049494</v>
+        <v>12.38310167198658</v>
       </c>
       <c r="J41" s="2" t="n">
         <v>0.7146941047175062</v>
@@ -2658,7 +2658,7 @@
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>419.1744451668981</v>
+        <v>419.174445166898</v>
       </c>
       <c r="E42" s="2" t="n">
         <v>25.8</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>55.02449394882009</v>
+        <v>55.02449391742635</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>23.6768871309057</v>
+        <v>23.67688712688496</v>
       </c>
       <c r="J42" s="2" t="n">
         <v>0.9556686811682706</v>
@@ -2725,10 +2725,10 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>23.48532294346204</v>
+        <v>23.48532301472335</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>55.30601209721097</v>
+        <v>55.30601215380953</v>
       </c>
       <c r="J43" s="2" t="n">
         <v>0.7419841596453609</v>
@@ -2743,7 +2743,7 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.0029094900209389</v>
+        <v>0.0029094900312419</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>393.175888902694</v>
+        <v>393.1758889026943</v>
       </c>
       <c r="E44" s="2" t="n">
         <v>19.5</v>
@@ -2778,10 +2778,10 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>35.0101092558788</v>
+        <v>35.01010917200365</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>25.931058593161</v>
+        <v>25.93105855792507</v>
       </c>
       <c r="J44" s="2" t="n">
         <v>2.633623604883756</v>
@@ -2796,7 +2796,7 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>-0.0464793444735024</v>
+        <v>-0.0464793444631961</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>49.18804479547161</v>
+        <v>49.18804503133477</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>12.27872906767675</v>
+        <v>12.27872909353246</v>
       </c>
       <c r="J45" s="2" t="n">
         <v>0.4851515203636359</v>
@@ -2849,7 +2849,7 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.0730598205857405</v>
+        <v>0.0730598204930125</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
@@ -2884,10 +2884,10 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>50.92365407559508</v>
+        <v>50.92365550605701</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>9.806275768982216</v>
+        <v>9.806276713361891</v>
       </c>
       <c r="J46" s="2" t="n">
         <v>0.0747420465119755</v>
@@ -2902,7 +2902,7 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.096114608249349</v>
+        <v>0.09611460400455581</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
@@ -2937,10 +2937,10 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>49.76664282805221</v>
+        <v>49.76664279490457</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>15.4819326378806</v>
+        <v>15.48193259133164</v>
       </c>
       <c r="J47" s="2" t="n">
         <v>0.5075576072771187</v>
@@ -2955,7 +2955,7 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>-0.0126520572965968</v>
+        <v>-0.0126520573069006</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>372.9722255578729</v>
+        <v>372.9722255578732</v>
       </c>
       <c r="E48" s="2" t="n">
         <v>13.8</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>52.30168121165394</v>
+        <v>52.30168129203528</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>27.20162786918543</v>
+        <v>27.20162805373186</v>
       </c>
       <c r="J48" s="2" t="n">
         <v>0.3390727924063561</v>
@@ -3008,7 +3008,7 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>0.0022935548433112</v>
+        <v>0.0022935547814944</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
@@ -3061,7 +3061,7 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>0.011318560176068</v>
+        <v>0.0113185601657682</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
@@ -3082,7 +3082,7 @@
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>364.8107824047813</v>
+        <v>364.8107824047804</v>
       </c>
       <c r="E50" s="2" t="n">
         <v>60</v>
@@ -3096,10 +3096,10 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>52.16489368283852</v>
+        <v>52.1648936802383</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>10.57232561535845</v>
+        <v>10.57232564303941</v>
       </c>
       <c r="J50" s="2" t="n">
         <v>0.3884383752219517</v>
@@ -3114,7 +3114,7 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>1.714778827357518</v>
+        <v>1.714778827295699</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>46.58871901396223</v>
+        <v>46.5887190325304</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>24.97273180932224</v>
+        <v>24.97273187999811</v>
       </c>
       <c r="J51" s="2" t="n">
         <v>0.2162454325099041</v>
@@ -3167,7 +3167,7 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-0.0370862846248416</v>
+        <v>-0.0370862846289644</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
@@ -3202,10 +3202,10 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>50.73631469167056</v>
+        <v>50.73631477243313</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>8.566707783910287</v>
+        <v>8.566707797494177</v>
       </c>
       <c r="J52" s="2" t="n">
         <v>0.6607899626004681</v>
@@ -3220,7 +3220,7 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>-0.0144298795963248</v>
+        <v>-0.0144298796478403</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
@@ -3258,7 +3258,7 @@
         <v>50.93823418234832</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>10.20390864595953</v>
+        <v>10.20390864370355</v>
       </c>
       <c r="J53" s="2" t="n">
         <v>0.1952270638936701</v>
@@ -3273,7 +3273,7 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.0675868625162675</v>
+        <v>0.0675868625265706</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>352.1249085842346</v>
+        <v>352.1249085842343</v>
       </c>
       <c r="E54" s="2" t="n">
         <v>0</v>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>30.33335353128142</v>
+        <v>30.33335353473473</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>24.70963796382662</v>
+        <v>24.70963798295186</v>
       </c>
       <c r="J54" s="2" t="n">
         <v>0</v>
@@ -3326,7 +3326,7 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-1.047930056869548</v>
+        <v>-1.047930056951973</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
@@ -3361,10 +3361,10 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>42.42273709710385</v>
+        <v>42.42273710004807</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>9.03585733126558</v>
+        <v>9.035857335734343</v>
       </c>
       <c r="J55" s="2" t="n">
         <v>0.3483373997759351</v>
@@ -3379,7 +3379,7 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>-0.0293021760513786</v>
+        <v>-0.0293021761028913</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
@@ -3400,7 +3400,7 @@
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>344.4726968174038</v>
+        <v>344.4726968174039</v>
       </c>
       <c r="E56" s="2" t="n">
         <v>105.5</v>
@@ -3414,10 +3414,10 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>41.22010919289527</v>
+        <v>41.22010908431373</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>14.01687637347819</v>
+        <v>14.01687644298336</v>
       </c>
       <c r="J56" s="2" t="n">
         <v>1.67872921694417</v>
@@ -3432,7 +3432,7 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-0.3796153910140771</v>
+        <v>-0.3796153903959114</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>48.48313166392384</v>
+        <v>48.48313183366961</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>26.19789054212075</v>
+        <v>26.19789054601214</v>
       </c>
       <c r="J57" s="2" t="n">
         <v>0.3359423949778098</v>
@@ -3520,10 +3520,10 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>28.35692069100982</v>
+        <v>28.35692071737463</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>27.44815137541359</v>
+        <v>27.44815135022232</v>
       </c>
       <c r="J58" s="2" t="n">
         <v>1.653008422598548</v>
@@ -3538,7 +3538,7 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-0.0139874692416193</v>
+        <v>-0.0139874692519222</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>337.5014318014976</v>
+        <v>337.5014318014991</v>
       </c>
       <c r="E59" s="2" t="n">
         <v>26</v>
@@ -3573,10 +3573,10 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>38.6317903313488</v>
+        <v>38.63179023705977</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>27.71108258040195</v>
+        <v>27.71108267960776</v>
       </c>
       <c r="J59" s="2" t="n">
         <v>0.6761643598881846</v>
@@ -3591,7 +3591,7 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-0.0023915764681421</v>
+        <v>-0.002391576385721</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>39.62140688979945</v>
+        <v>39.62140690004976</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>32.55773089204103</v>
+        <v>32.55773091442138</v>
       </c>
       <c r="J60" s="2" t="n">
         <v>0.5852551952054829</v>
@@ -3665,7 +3665,7 @@
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>334.2416530707876</v>
+        <v>334.2416530707877</v>
       </c>
       <c r="E61" s="2" t="n">
         <v>32.65</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>50.76748373407746</v>
+        <v>50.76748480707426</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>8.232681164246451</v>
+        <v>8.232681516660033</v>
       </c>
       <c r="J61" s="2" t="n">
         <v>0.7607929230308067</v>
@@ -3697,7 +3697,7 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.0384647188495408</v>
+        <v>0.0384647182931859</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>333.0183763969388</v>
+        <v>333.0183763969389</v>
       </c>
       <c r="E62" s="2" t="n">
         <v>14.75</v>
@@ -3732,10 +3732,10 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>24.76761666148377</v>
+        <v>24.76761654329372</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>24.9465641163318</v>
+        <v>24.9465641585789</v>
       </c>
       <c r="J62" s="2" t="n">
         <v>3.092441738586137</v>
@@ -3750,7 +3750,7 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-0.1118197576540327</v>
+        <v>-0.1118197576025184</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
@@ -3771,7 +3771,7 @@
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>331.4637963577784</v>
+        <v>331.4637963577783</v>
       </c>
       <c r="E63" s="2" t="n">
         <v>27.7</v>
@@ -3785,10 +3785,10 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>32.41645748888907</v>
+        <v>32.41645746766615</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>19.27713960663537</v>
+        <v>19.27713964822369</v>
       </c>
       <c r="J63" s="2" t="n">
         <v>0.951770542148195</v>
@@ -3803,7 +3803,7 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-0.2440892927937312</v>
+        <v>-0.2440892928555463</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
@@ -3838,10 +3838,10 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>39.89126307860599</v>
+        <v>39.89126324080706</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>16.13051192245653</v>
+        <v>16.13051195168057</v>
       </c>
       <c r="J64" s="2" t="n">
         <v>0.7020971486000142</v>
@@ -3856,7 +3856,7 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-0.1374133380784252</v>
+        <v>-0.1374133380681245</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>322.1183274563289</v>
+        <v>322.1183274563284</v>
       </c>
       <c r="E65" s="2" t="n">
         <v>68.5</v>
@@ -3891,10 +3891,10 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>43.23004439744802</v>
+        <v>43.23004444130681</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>15.93433186530655</v>
+        <v>15.93433192821562</v>
       </c>
       <c r="J65" s="2" t="n">
         <v>0.7089900705847003</v>
@@ -3909,7 +3909,7 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-0.3721517096958779</v>
+        <v>-0.3721517101080017</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
@@ -3944,10 +3944,10 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>44.62162333988528</v>
+        <v>44.62162323283446</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>21.31044172031665</v>
+        <v>21.31044175539902</v>
       </c>
       <c r="J66" s="2" t="n">
         <v>0.5345146938859737</v>
@@ -3962,7 +3962,7 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-0.0544585819252956</v>
+        <v>-0.0544585818943868</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
@@ -3997,10 +3997,10 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>44.31603431326939</v>
+        <v>44.31604735532043</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>22.81993488272189</v>
+        <v>22.81993943831284</v>
       </c>
       <c r="J67" s="2" t="n">
         <v>0.4719151337708807</v>
@@ -4015,7 +4015,7 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.0012891737087281</v>
+        <v>0.0012891706281601</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>43.16358179864906</v>
+        <v>43.16358200312141</v>
       </c>
       <c r="I68" s="2" t="n">
         <v>10.65137082042527</v>
@@ -4068,7 +4068,7 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-0.0169469591795851</v>
+        <v>-0.0169469592001902</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
@@ -4089,7 +4089,7 @@
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>310.427635276651</v>
+        <v>310.4276352766508</v>
       </c>
       <c r="E69" s="2" t="n">
         <v>17.1</v>
@@ -4103,10 +4103,10 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>43.29169737585897</v>
+        <v>43.29169746622856</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>18.63885063998946</v>
+        <v>18.6388506235312</v>
       </c>
       <c r="J69" s="2" t="n">
         <v>0.911360284080754</v>
@@ -4121,7 +4121,7 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.0005311494069418</v>
+        <v>0.0005311493863374</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
@@ -4156,10 +4156,10 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>43.14906620416949</v>
+        <v>43.14906615127083</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>23.50223984498413</v>
+        <v>23.50223988705314</v>
       </c>
       <c r="J70" s="2" t="n">
         <v>0.5120523351121652</v>
@@ -4174,7 +4174,7 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.1264880515905116</v>
+        <v>0.1264880517141436</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>44.43546668014309</v>
+        <v>44.43546668675432</v>
       </c>
       <c r="I71" s="2" t="n">
         <v>18.87600789052682</v>
@@ -4227,7 +4227,7 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-0.1577845763663179</v>
+        <v>-0.1577845764281358</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
@@ -4248,7 +4248,7 @@
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>297.8901220404101</v>
+        <v>297.8901220404103</v>
       </c>
       <c r="E72" s="2" t="n">
         <v>13.05</v>
@@ -4262,10 +4262,10 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>44.63866019244454</v>
+        <v>44.63866022279278</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>20.77728971900297</v>
+        <v>20.77728980728407</v>
       </c>
       <c r="J72" s="2" t="n">
         <v>0.502963476140964</v>
@@ -4280,7 +4280,7 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>3.172226460564781e-05</v>
+        <v>3.172225430302794e-05</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
@@ -4315,10 +4315,10 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>51.56782478579483</v>
+        <v>51.5678248157296</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>12.99633619565235</v>
+        <v>12.99633628037481</v>
       </c>
       <c r="J73" s="2" t="n">
         <v>1.603768348902477</v>
@@ -4333,7 +4333,7 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-0.0309995603711438</v>
+        <v>-0.0309995603814466</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
@@ -4354,7 +4354,7 @@
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>292.9792414255554</v>
+        <v>292.9792414255561</v>
       </c>
       <c r="E74" s="2" t="n">
         <v>699</v>
@@ -4368,10 +4368,10 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>44.12876807303724</v>
+        <v>44.12876814630479</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>11.31046960697478</v>
+        <v>11.31046961010666</v>
       </c>
       <c r="J74" s="2" t="n">
         <v>0.4262569204174543</v>
@@ -4386,7 +4386,7 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-2.325496129776147</v>
+        <v>-2.325496132454834</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
@@ -4407,7 +4407,7 @@
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>292.2727637231952</v>
+        <v>292.2727637231951</v>
       </c>
       <c r="E75" s="2" t="n">
         <v>276.5</v>
@@ -4421,10 +4421,10 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>27.60065125312337</v>
+        <v>27.6006514368144</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>39.5913450503996</v>
+        <v>39.59134505989268</v>
       </c>
       <c r="J75" s="2" t="n">
         <v>1.101667727907232</v>
@@ -4439,7 +4439,7 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-0.7220464001343458</v>
+        <v>-0.7220464013706298</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>290.5563946990527</v>
+        <v>290.5563946990526</v>
       </c>
       <c r="E76" s="2" t="n">
         <v>9.970000000000001</v>
@@ -4474,10 +4474,10 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>39.69797755024023</v>
+        <v>39.69797596997519</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>22.84733803930289</v>
+        <v>22.84733814630626</v>
       </c>
       <c r="J76" s="2" t="n">
         <v>0.4376298873520786</v>
@@ -4492,7 +4492,7 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>0.0090585002101527</v>
+        <v>0.009058500241062599</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>284.5936052404758</v>
+        <v>284.5936052404757</v>
       </c>
       <c r="E77" s="2" t="n">
         <v>26.65</v>
@@ -4527,10 +4527,10 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>48.14675888224799</v>
+        <v>48.14675887273457</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>22.71983742039029</v>
+        <v>22.71983757968933</v>
       </c>
       <c r="J77" s="2" t="n">
         <v>0.5794892233667036</v>
@@ -4545,7 +4545,7 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>0.1215759977745007</v>
+        <v>0.1215759979187395</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
@@ -4580,10 +4580,10 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>51.21739120138025</v>
+        <v>51.21739120090434</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>11.48208650327126</v>
+        <v>11.48208651725725</v>
       </c>
       <c r="J78" s="2" t="n">
         <v>1.508667725671662</v>
@@ -4598,7 +4598,7 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.6964450159931144</v>
+        <v>0.6964450160034265</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
@@ -4633,10 +4633,10 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>36.72531338978541</v>
+        <v>36.72531320496911</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>37.98356625873164</v>
+        <v>37.98356660496544</v>
       </c>
       <c r="J79" s="2" t="n">
         <v>0.7091782403611994</v>
@@ -4651,7 +4651,7 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>0.3264349114034752</v>
+        <v>0.3264349120216505</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
@@ -4672,7 +4672,7 @@
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>264.66307813358</v>
+        <v>264.6630781335797</v>
       </c>
       <c r="E80" s="2" t="n">
         <v>47</v>
@@ -4686,10 +4686,10 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>42.71665610596107</v>
+        <v>42.71665586666957</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>9.140662847124412</v>
+        <v>9.140662893558956</v>
       </c>
       <c r="J80" s="2" t="n">
         <v>0.918806715129435</v>
@@ -4704,7 +4704,7 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-0.0378001686748628</v>
+        <v>-0.0378001681185071</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
@@ -4739,10 +4739,10 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>50.21515309932448</v>
+        <v>50.21515326515548</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>12.34245574662815</v>
+        <v>12.34245617887821</v>
       </c>
       <c r="J81" s="2" t="n">
         <v>0.4095651925805789</v>
@@ -4757,7 +4757,7 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>-0.012616557779775</v>
+        <v>-0.0126165578931077</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
@@ -4792,10 +4792,10 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>45.35370197292813</v>
+        <v>45.35370215381646</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>16.77278618428673</v>
+        <v>16.77278616033155</v>
       </c>
       <c r="J82" s="2" t="n">
         <v>0.4670247023880471</v>
@@ -4810,7 +4810,7 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-0.2187264450002918</v>
+        <v>-0.2187264451033156</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
@@ -4845,10 +4845,10 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>31.90709045651516</v>
+        <v>31.90709043628356</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>22.61088599681586</v>
+        <v>22.6108859698442</v>
       </c>
       <c r="J83" s="2" t="n">
         <v>1.267694664083302</v>
@@ -4898,10 +4898,10 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>40.38847242648038</v>
+        <v>40.38847264881744</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>32.06027482614487</v>
+        <v>32.06027476096221</v>
       </c>
       <c r="J84" s="2" t="n">
         <v>0.6225557950428553</v>
@@ -4937,7 +4937,7 @@
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>251.6014864706753</v>
+        <v>251.6014864706743</v>
       </c>
       <c r="E85" s="2" t="n">
         <v>66</v>
@@ -4951,10 +4951,10 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>48.3759111283575</v>
+        <v>48.37591118037257</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>12.05625700059126</v>
+        <v>12.05625701010428</v>
       </c>
       <c r="J85" s="2" t="n">
         <v>0.2763589828495598</v>
@@ -4969,7 +4969,7 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-0.1251747436752714</v>
+        <v>-0.125174743737088</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
@@ -5004,10 +5004,10 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>39.65414004088515</v>
+        <v>39.6541399191126</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>7.5580309168634</v>
+        <v>7.558030916863396</v>
       </c>
       <c r="J86" s="2" t="n">
         <v>2.986749443468509</v>
@@ -5022,7 +5022,7 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>0.0146174883231166</v>
+        <v>0.0146174883849338</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
@@ -5043,7 +5043,7 @@
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>247.4306371673675</v>
+        <v>247.4306371673674</v>
       </c>
       <c r="E87" s="2" t="n">
         <v>10.8</v>
@@ -5060,7 +5060,7 @@
         <v>33.06635877516952</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>23.3368946476919</v>
+        <v>23.33689467604703</v>
       </c>
       <c r="J87" s="2" t="n">
         <v>0.4179182929817769</v>
@@ -5110,10 +5110,10 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>48.71433749644433</v>
+        <v>48.71433743579543</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>5.930345808802407</v>
+        <v>5.930345847115438</v>
       </c>
       <c r="J88" s="2" t="n">
         <v>0.436274081950618</v>
@@ -5128,7 +5128,7 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>0.0415502903731948</v>
+        <v>0.0415502904453151</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
@@ -5163,10 +5163,10 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>43.8817042657624</v>
+        <v>43.88170428445039</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>15.0818304795585</v>
+        <v>15.08183058431626</v>
       </c>
       <c r="J89" s="2" t="n">
         <v>0.5186073575128568</v>
@@ -5181,7 +5181,7 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>0.0155526809337908</v>
+        <v>0.0155526809358521</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
         <v>42.16577189361502</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>10.2949763215147</v>
+        <v>10.29497635124557</v>
       </c>
       <c r="J90" s="2" t="n">
         <v>0.168613957688645</v>
@@ -5234,7 +5234,7 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>0.031078309207495</v>
+        <v>0.0310783092013129</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
@@ -5255,7 +5255,7 @@
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>232.4316965804152</v>
+        <v>232.4316965804149</v>
       </c>
       <c r="E91" s="2" t="n">
         <v>102</v>
@@ -5269,10 +5269,10 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>49.16387781592628</v>
+        <v>49.16387774062459</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>14.44930207695184</v>
+        <v>14.44930207460586</v>
       </c>
       <c r="J91" s="2" t="n">
         <v>1.351277911539894</v>
@@ -5287,7 +5287,7 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.3594726392573232</v>
+        <v>0.3594726396694385</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
@@ -5322,10 +5322,10 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>34.03165126832047</v>
+        <v>34.03165134729996</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>24.15595550586509</v>
+        <v>24.15595550882902</v>
       </c>
       <c r="J92" s="2" t="n">
         <v>0.2697946046931946</v>
@@ -5340,7 +5340,7 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-0.0216342540739243</v>
+        <v>-0.0216342541357427</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
@@ -5375,10 +5375,10 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>32.59704691572874</v>
+        <v>32.59704687693366</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>29.78140831715586</v>
+        <v>29.78140838246116</v>
       </c>
       <c r="J93" s="2" t="n">
         <v>0.9539468689393882</v>
@@ -5393,7 +5393,7 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-0.0478241144263929</v>
+        <v>-0.0478241144160887</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         <v>46.59781347622856</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>14.55126456953445</v>
+        <v>14.5512646240608</v>
       </c>
       <c r="J94" s="2" t="n">
         <v>0.5180395055277867</v>
@@ -5446,7 +5446,7 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-0.24152616081207</v>
+        <v>-0.241526160709038</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>43.75689453703884</v>
+        <v>43.75689456264242</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>14.52606952527272</v>
+        <v>14.52606955811724</v>
       </c>
       <c r="J95" s="2" t="n">
         <v>1.061136792964763</v>
@@ -5499,7 +5499,7 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-0.008398986498580299</v>
+        <v>-0.0083989865191862</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
@@ -5534,10 +5534,10 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>48.64578567582122</v>
+        <v>48.6457856648475</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>12.18296457283881</v>
+        <v>12.18296464062828</v>
       </c>
       <c r="J96" s="2" t="n">
         <v>0.2249250096795675</v>
@@ -5552,7 +5552,7 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-0.0838127958451875</v>
+        <v>-0.08381279588639851</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
@@ -5587,10 +5587,10 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>33.17979778344731</v>
+        <v>33.17979786824418</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>8.769809614254433</v>
+        <v>8.769809602556821</v>
       </c>
       <c r="J97" s="2" t="n">
         <v>0.7535309221377681</v>
@@ -5605,7 +5605,7 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-0.4561794849406828</v>
+        <v>-0.4561794846315825</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
@@ -5640,7 +5640,7 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>40.61848543601389</v>
+        <v>40.61848534278261</v>
       </c>
       <c r="I98" s="2" t="n">
         <v>17.86580193502385</v>
@@ -5693,10 +5693,10 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>50.91200453318152</v>
+        <v>50.91200446564194</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>8.920657514251682</v>
+        <v>8.92065751425168</v>
       </c>
       <c r="J99" s="2" t="n">
         <v>0.603459583538285</v>
@@ -5711,7 +5711,7 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>0.3059918048370221</v>
+        <v>0.3059918046846929</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
@@ -5746,10 +5746,10 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>34.86046143660859</v>
+        <v>34.86046120086584</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>32.47825081832897</v>
+        <v>32.47825076977574</v>
       </c>
       <c r="J100" s="2" t="n">
         <v>0.7728841266485443</v>
@@ -5764,7 +5764,7 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>0.0029119068377951</v>
+        <v>0.002911906848098</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
@@ -5802,7 +5802,7 @@
         <v>41.08444409117836</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>10.97575315166562</v>
+        <v>10.97575308408577</v>
       </c>
       <c r="J101" s="2" t="n">
         <v>0.8187801994017417</v>
@@ -5817,7 +5817,7 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>0.0050552602008418</v>
+        <v>0.0050552602111418</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
@@ -5852,10 +5852,10 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>39.5403749382553</v>
+        <v>39.5403746782918</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>23.16157988497739</v>
+        <v>23.16158012845588</v>
       </c>
       <c r="J102" s="2" t="n">
         <v>0.6938625427939001</v>
@@ -5870,7 +5870,7 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.0581086236187191</v>
+        <v>-0.0581086230829653</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
@@ -5891,7 +5891,7 @@
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>210.8729195606529</v>
+        <v>210.8729195606531</v>
       </c>
       <c r="E103" s="2" t="n">
         <v>23.05</v>
@@ -5905,10 +5905,10 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>45.25963939602129</v>
+        <v>45.25963943182494</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>5.119036127622759</v>
+        <v>5.119036154578149</v>
       </c>
       <c r="J103" s="2" t="n">
         <v>0.8622069614414106</v>
@@ -5923,7 +5923,7 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-0.0033726784275606</v>
+        <v>-0.0033726784687696</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
@@ -5961,7 +5961,7 @@
         <v>50.43547673679654</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>18.06665914057961</v>
+        <v>18.06665908503258</v>
       </c>
       <c r="J104" s="2" t="n">
         <v>0.9288049767465556</v>
@@ -5997,7 +5997,7 @@
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>194.2179619016075</v>
+        <v>194.2179619016106</v>
       </c>
       <c r="E105" s="2" t="n">
         <v>64.40000000000001</v>
@@ -6011,10 +6011,10 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>51.18018452391785</v>
+        <v>51.18018451381249</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>21.54249097412362</v>
+        <v>21.542490833729</v>
       </c>
       <c r="J105" s="2" t="n">
         <v>1.504848647200643</v>
@@ -6029,7 +6029,7 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-1.184543157910109</v>
+        <v>-1.184543157539203</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
@@ -6064,10 +6064,10 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>42.75937490525939</v>
+        <v>42.75937508015001</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>16.36644319748243</v>
+        <v>16.36644321871258</v>
       </c>
       <c r="J106" s="2" t="n">
         <v>1.081609927212568</v>
@@ -6082,7 +6082,7 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>0.0069930216143574</v>
+        <v>0.0069930215937528</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
@@ -6117,10 +6117,10 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>45.46547026813975</v>
+        <v>45.46547030186201</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>13.19563537735114</v>
+        <v>13.19563541064757</v>
       </c>
       <c r="J107" s="2" t="n">
         <v>0.5325164438786336</v>
@@ -6135,7 +6135,7 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-0.0114865284899529</v>
+        <v>-0.0114865286135915</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>177.8432355317165</v>
+        <v>177.8432355317164</v>
       </c>
       <c r="E108" s="2" t="n">
         <v>196</v>
@@ -6170,7 +6170,7 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>43.30531210020706</v>
+        <v>43.30531215740378</v>
       </c>
       <c r="I108" s="2" t="n">
         <v>10.00399064412504</v>
@@ -6223,10 +6223,10 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>48.39438040279474</v>
+        <v>48.39437996819087</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>12.5414528936279</v>
+        <v>12.54145300237842</v>
       </c>
       <c r="J109" s="2" t="n">
         <v>0.5535224586928081</v>
@@ -6241,7 +6241,7 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>0.0512900794089901</v>
+        <v>0.0512900796150477</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
@@ -6276,7 +6276,7 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>52.77989777201535</v>
+        <v>52.77989777541445</v>
       </c>
       <c r="I110" s="2" t="n">
         <v>9.1671226089423</v>
@@ -6294,7 +6294,7 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>2.690341496505717</v>
+        <v>2.690341496361478</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
@@ -6332,7 +6332,7 @@
         <v>45.75353411473413</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>11.43605780234731</v>
+        <v>11.43605779883075</v>
       </c>
       <c r="J111" s="2" t="n">
         <v>0.0001400550416313</v>
@@ -6385,7 +6385,7 @@
         <v>51.91879873819772</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>19.44384807920188</v>
+        <v>19.44384807457648</v>
       </c>
       <c r="J112" s="2" t="n">
         <v>0.2236906510034263</v>
@@ -6400,7 +6400,7 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>0.0404375592194801</v>
+        <v>0.040437559178269</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
@@ -6435,10 +6435,10 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>47.78896417967887</v>
+        <v>47.78896365929295</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>15.68770208826056</v>
+        <v>15.68770203533845</v>
       </c>
       <c r="J113" s="2" t="n">
         <v>1.138063168865906</v>
@@ -6453,7 +6453,7 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>0.0102298855288995</v>
+        <v>0.0102298858998013</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>161.8770216573484</v>
+        <v>161.8770216573474</v>
       </c>
       <c r="E114" s="2" t="n">
         <v>26.7</v>
@@ -6488,10 +6488,10 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>32.86232829554959</v>
+        <v>32.86232830231734</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>19.10831854223087</v>
+        <v>19.10831852076622</v>
       </c>
       <c r="J114" s="2" t="n">
         <v>0.3016058633221153</v>
@@ -6506,7 +6506,7 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-0.1218205302396243</v>
+        <v>-0.1218205302602301</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
@@ -6541,10 +6541,10 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>49.90280746149206</v>
+        <v>49.90280756175169</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>12.69467963153254</v>
+        <v>12.69467972535677</v>
       </c>
       <c r="J115" s="2" t="n">
         <v>1.087615949355959</v>
@@ -6559,7 +6559,7 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-0.0005648757909755</v>
+        <v>-0.0005648758012771</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
@@ -6594,10 +6594,10 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>38.80466856445916</v>
+        <v>38.80466804510702</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>9.519760066748011</v>
+        <v>9.51976021130945</v>
       </c>
       <c r="J116" s="2" t="n">
         <v>0.9554569055577288</v>
@@ -6612,7 +6612,7 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>0.0102867784494589</v>
+        <v>0.0102867785153978</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
@@ -6647,10 +6647,10 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>41.02453311432241</v>
+        <v>41.02453300258299</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>10.16589349199025</v>
+        <v>10.16589351099681</v>
       </c>
       <c r="J117" s="2" t="n">
         <v>0.1011474815970939</v>
@@ -6665,7 +6665,7 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>-0.0017563047307236</v>
+        <v>-0.0017563047101163</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
@@ -6700,10 +6700,10 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>36.77541197846822</v>
+        <v>36.77541204876096</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>23.0372737273773</v>
+        <v>23.03727374614221</v>
       </c>
       <c r="J118" s="2" t="n">
         <v>0.1997971702293157</v>
@@ -6718,7 +6718,7 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>-0.0115572104005615</v>
+        <v>-0.0115572104211656</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
@@ -6753,10 +6753,10 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>37.80698432934248</v>
+        <v>37.80698450167327</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>17.25404834173696</v>
+        <v>17.25404851467422</v>
       </c>
       <c r="J119" s="2" t="n">
         <v>0.09485171628344451</v>
@@ -6771,7 +6771,7 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>-0.014061397039644</v>
+        <v>-0.0140613970190381</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
@@ -6806,10 +6806,10 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>39.10305944947053</v>
+        <v>39.10305957349571</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>15.84860772938364</v>
+        <v>15.84860774067127</v>
       </c>
       <c r="J120" s="2" t="n">
         <v>0.2898815301299903</v>
@@ -6824,7 +6824,7 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>0.0639195305219997</v>
+        <v>0.06391953048078711</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
@@ -6845,7 +6845,7 @@
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>150.6907412260265</v>
+        <v>150.6907412260264</v>
       </c>
       <c r="E121" s="2" t="n">
         <v>79.59999999999999</v>
@@ -6859,10 +6859,10 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>41.33665312453917</v>
+        <v>41.33665306039034</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>10.76942217858215</v>
+        <v>10.76942234848532</v>
       </c>
       <c r="J121" s="2" t="n">
         <v>0.5036580712732786</v>
@@ -6877,7 +6877,7 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>0.1293157686558813</v>
+        <v>0.1293157691710231</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
@@ -6912,10 +6912,10 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>46.1734966564245</v>
+        <v>46.17349648567914</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>8.802496416839771</v>
+        <v>8.802496472927102</v>
       </c>
       <c r="J122" s="2" t="n">
         <v>0.3445227478682101</v>
@@ -6930,7 +6930,7 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>0.0059497130093179</v>
+        <v>0.005949713040227</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
@@ -6951,7 +6951,7 @@
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>143.216443171296</v>
+        <v>143.2164431712961</v>
       </c>
       <c r="E123" s="2" t="n">
         <v>14.35</v>
@@ -6965,10 +6965,10 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>47.14649695124344</v>
+        <v>47.14649688258773</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>11.92050054080074</v>
+        <v>11.92050045338421</v>
       </c>
       <c r="J123" s="2" t="n">
         <v>0.5152589055244483</v>
@@ -6983,7 +6983,7 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>-0.0076900530347278</v>
+        <v>-0.0076900530141223</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
@@ -7018,10 +7018,10 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>43.64610467316226</v>
+        <v>43.64610464171341</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>19.23217670651324</v>
+        <v>19.23217675365634</v>
       </c>
       <c r="J124" s="2" t="n">
         <v>0.1051216414652538</v>
@@ -7036,7 +7036,7 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>0.0159319404163587</v>
+        <v>0.0159319405502945</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
@@ -7071,10 +7071,10 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>36.18091045899258</v>
+        <v>36.18091053745876</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>9.354981190098441</v>
+        <v>9.354981228073022</v>
       </c>
       <c r="J125" s="2" t="n">
         <v>0.2862937149337433</v>
@@ -7089,7 +7089,7 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>-0.0036221740890226</v>
+        <v>-0.0036221741302361</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
@@ -7124,10 +7124,10 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>39.06292275115396</v>
+        <v>39.06292270622599</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>9.452739815720539</v>
+        <v>9.452739850796</v>
       </c>
       <c r="J126" s="2" t="n">
         <v>0.7371579717980277</v>
@@ -7142,7 +7142,7 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>-0.0005736163216236</v>
+        <v>-0.0005736163092595001</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
@@ -7177,10 +7177,10 @@
         <v>0</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>50.9273266867197</v>
+        <v>50.927326741284</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>10.55419107212293</v>
+        <v>10.55419107618756</v>
       </c>
       <c r="J127" s="2" t="n">
         <v>0.7333678287830576</v>
@@ -7195,7 +7195,7 @@
         <v>-1</v>
       </c>
       <c r="N127" s="2" t="n">
-        <v>-0.0101972522726693</v>
+        <v>-0.0101972522932754</v>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
@@ -7230,10 +7230,10 @@
         <v>0</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>39.96116768194389</v>
+        <v>39.96116754927892</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>18.30873215953499</v>
+        <v>18.30873243307893</v>
       </c>
       <c r="J128" s="2" t="n">
         <v>0.5127334465195246</v>
@@ -7248,7 +7248,7 @@
         <v>-1</v>
       </c>
       <c r="N128" s="2" t="n">
-        <v>0.0015208744634838</v>
+        <v>0.0015208746901456</v>
       </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
@@ -7283,10 +7283,10 @@
         <v>0</v>
       </c>
       <c r="H129" s="2" t="n">
-        <v>41.89733815074717</v>
+        <v>41.89733806673743</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>14.10139027183106</v>
+        <v>14.10139034621174</v>
       </c>
       <c r="J129" s="2" t="n">
         <v>0.9779548285610944</v>
@@ -7301,7 +7301,7 @@
         <v>-1</v>
       </c>
       <c r="N129" s="2" t="n">
-        <v>-0.0484924271076976</v>
+        <v>-0.0484924270252753</v>
       </c>
       <c r="O129" s="2" t="inlineStr">
         <is>
@@ -7322,7 +7322,7 @@
         <v/>
       </c>
       <c r="D130" s="2" t="n">
-        <v>89.49831170708894</v>
+        <v>89.49831170708893</v>
       </c>
       <c r="E130" s="2" t="n">
         <v>45.6</v>
@@ -7339,7 +7339,7 @@
         <v>49.14989578507964</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>13.93374916693373</v>
+        <v>13.93374915212161</v>
       </c>
       <c r="J130" s="2" t="n">
         <v>0.7975212146144058</v>
@@ -7375,7 +7375,7 @@
         <v/>
       </c>
       <c r="D131" s="2" t="n">
-        <v>88.34879135601571</v>
+        <v>88.3487913560156</v>
       </c>
       <c r="E131" s="2" t="n">
         <v>9.4</v>
@@ -7389,10 +7389,10 @@
         <v>0</v>
       </c>
       <c r="H131" s="2" t="n">
-        <v>42.81461567884486</v>
+        <v>42.81461527802914</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>15.5558706878708</v>
+        <v>15.55587129457165</v>
       </c>
       <c r="J131" s="2" t="n">
         <v>0.5619201813244366</v>
@@ -7407,7 +7407,7 @@
         <v>-1</v>
       </c>
       <c r="N131" s="2" t="n">
-        <v>-0.008275869476349</v>
+        <v>-0.008275869332108899</v>
       </c>
       <c r="O131" s="2" t="inlineStr">
         <is>
@@ -7442,10 +7442,10 @@
         <v>0</v>
       </c>
       <c r="H132" s="2" t="n">
-        <v>51.74505613837026</v>
+        <v>51.74505581842296</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>11.77863272633815</v>
+        <v>11.7786327326755</v>
       </c>
       <c r="J132" s="2" t="n">
         <v>0.6524428229882353</v>
@@ -7460,7 +7460,7 @@
         <v>-1</v>
       </c>
       <c r="N132" s="2" t="n">
-        <v>0.016034486672102</v>
+        <v>0.0160344867030118</v>
       </c>
       <c r="O132" s="2" t="inlineStr">
         <is>
@@ -7495,10 +7495,10 @@
         <v>0</v>
       </c>
       <c r="H133" s="2" t="n">
-        <v>44.53314503206301</v>
+        <v>44.53314504609418</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>12.80569380572918</v>
+        <v>12.80569386850856</v>
       </c>
       <c r="J133" s="2" t="n">
         <v>0.2469258623831483</v>
@@ -7513,7 +7513,7 @@
         <v>-1</v>
       </c>
       <c r="N133" s="2" t="n">
-        <v>-0.0580568853523309</v>
+        <v>-0.0580568853626315</v>
       </c>
       <c r="O133" s="2" t="inlineStr">
         <is>

--- a/output/full_scan/batch_seq1_2026-09-24.xlsx
+++ b/output/full_scan/batch_seq1_2026-09-24.xlsx
@@ -552,7 +552,7 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>76.76980525541725</v>
+        <v>76.76980524038702</v>
       </c>
       <c r="I2" s="2" t="n">
         <v>31.4168015702786</v>
@@ -570,7 +570,7 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>24.49570838768908</v>
+        <v>24.49570838713284</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
@@ -605,10 +605,10 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>79.89106143081827</v>
+        <v>79.89106144724846</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>53.06968890241327</v>
+        <v>53.06968897342369</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>2.741649652972179</v>
@@ -623,7 +623,7 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>1.590931853720629</v>
+        <v>1.590931853431317</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
@@ -658,10 +658,10 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>58.61440598226877</v>
+        <v>58.61440390091276</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>17.18896536541293</v>
+        <v>17.18896616509328</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>1.283795586748832</v>
@@ -676,7 +676,7 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.0340843738862658</v>
+        <v>0.034084376612413</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>56.55433808511896</v>
+        <v>56.55433813085726</v>
       </c>
       <c r="I5" s="2" t="n">
         <v>40.34462239767203</v>
@@ -729,7 +729,7 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>-0.0751935973454885</v>
+        <v>-0.0751935973521636</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>767.8038587209888</v>
+        <v>767.8038587209887</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>35.7</v>
@@ -764,10 +764,10 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>60.93299614592757</v>
+        <v>60.93299628370752</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>26.89643566749574</v>
+        <v>26.89643574083017</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>0.999049460502734</v>
@@ -782,7 +782,7 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.0082772938571382</v>
+        <v>0.0082772937792526</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>739.1887917528753</v>
+        <v>739.1887917528754</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>238</v>
@@ -817,10 +817,10 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>58.09717154455284</v>
+        <v>58.09717155545822</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>23.99712473988518</v>
+        <v>23.99712475800661</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>0.7949632640336151</v>
@@ -835,7 +835,7 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>-1.694069483463693</v>
+        <v>-1.694069483652855</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
@@ -870,10 +870,10 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>75.49115445273235</v>
+        <v>75.49115435857719</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>45.93921664763305</v>
+        <v>45.93921666616041</v>
       </c>
       <c r="J8" s="2" t="n">
         <v>0.3006969482605902</v>
@@ -888,7 +888,7 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.06822995720925989</v>
+        <v>0.06822995725377499</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>65.72105379229193</v>
+        <v>65.72105380200219</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>37.09592363131511</v>
+        <v>37.09592355373212</v>
       </c>
       <c r="J9" s="2" t="n">
         <v>0.7737003345632983</v>
@@ -941,7 +941,7 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.4556074240692371</v>
+        <v>0.4556074240469865</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>-0.0569605197490807</v>
+        <v>-0.0569605197300099</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
@@ -1029,10 +1029,10 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>58.52601513452927</v>
+        <v>58.52601507359403</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>31.75787830596096</v>
+        <v>31.75787825517412</v>
       </c>
       <c r="J11" s="2" t="n">
         <v>0.6525081178999347</v>
@@ -1047,7 +1047,7 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.09325906346322931</v>
+        <v>0.0932590635299913</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>60.71553072717938</v>
+        <v>60.71553058892556</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>34.27801534311887</v>
+        <v>34.2780154588573</v>
       </c>
       <c r="J12" s="2" t="n">
         <v>0.4865206968699114</v>
@@ -1100,7 +1100,7 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>-0.341278136417837</v>
+        <v>-0.3412781364559758</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -1135,10 +1135,10 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>60.28988319413902</v>
+        <v>60.28988236524086</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>18.11439463217432</v>
+        <v>18.11439440416688</v>
       </c>
       <c r="J13" s="2" t="n">
         <v>1.438336874983999</v>
@@ -1153,7 +1153,7 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.0821446363620538</v>
+        <v>0.0821446368405189</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>53.53620403183438</v>
+        <v>53.53620410186679</v>
       </c>
       <c r="I14" s="2" t="n">
         <v>21.43000327057417</v>
@@ -1206,7 +1206,7 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.001400773993717</v>
+        <v>0.0014007739825906</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>52.08992669373536</v>
+        <v>52.08992664370918</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>10.26933187518033</v>
+        <v>10.26933189821618</v>
       </c>
       <c r="J15" s="2" t="n">
         <v>0.6639548655403902</v>
@@ -1259,7 +1259,7 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0.07017635764339759</v>
+        <v>0.07017635819976679</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1294,10 +1294,10 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>51.63017684017526</v>
+        <v>51.63017687344052</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>28.26579695102428</v>
+        <v>28.26579698882282</v>
       </c>
       <c r="J16" s="2" t="n">
         <v>0.5053244878320772</v>
@@ -1312,7 +1312,7 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>-0.6345949737597965</v>
+        <v>-0.634594973815424</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1347,10 +1347,10 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>71.14387143480535</v>
+        <v>71.14387138057266</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>36.11969027829939</v>
+        <v>36.11969026283181</v>
       </c>
       <c r="J17" s="2" t="n">
         <v>0.4134116033172695</v>
@@ -1365,7 +1365,7 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>0.1645810011723649</v>
+        <v>0.1645810012391424</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>53.23083455005789</v>
+        <v>53.23083461253161</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>22.9516400415005</v>
+        <v>22.95164004150051</v>
       </c>
       <c r="J18" s="2" t="n">
         <v>0.5460843204995706</v>
@@ -1418,7 +1418,7 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>-0.3531246933425762</v>
+        <v>-0.3531246934315972</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         <v>51.93921035606791</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>23.12381053684191</v>
+        <v>23.12381055434743</v>
       </c>
       <c r="J19" s="2" t="n">
         <v>0.7842704691768611</v>
@@ -1471,7 +1471,7 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.0027103237888756</v>
+        <v>0.0027103238000055</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
@@ -1506,10 +1506,10 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>44.40915747510478</v>
+        <v>44.40915745514376</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>15.14464573862796</v>
+        <v>15.14464573332165</v>
       </c>
       <c r="J20" s="2" t="n">
         <v>0.2270158080671501</v>
@@ -1524,7 +1524,7 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>-0.0742537835436735</v>
+        <v>-0.0742537834991648</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>60.70055988039058</v>
+        <v>60.70055989509937</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>41.10032647486013</v>
+        <v>41.10032645734289</v>
       </c>
       <c r="J21" s="2" t="n">
         <v>1.013911217114202</v>
@@ -1577,7 +1577,7 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0.0752580332551296</v>
+        <v>0.075258033252905</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
         <v>54.08287236493935</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>15.87081657321302</v>
+        <v>15.87081671068779</v>
       </c>
       <c r="J22" s="2" t="n">
         <v>0.407092049387347</v>
@@ -1665,10 +1665,10 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>56.79220558377262</v>
+        <v>56.79220563949485</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>15.71171701028789</v>
+        <v>15.71171699557782</v>
       </c>
       <c r="J23" s="2" t="n">
         <v>1.105566558177927</v>
@@ -1683,7 +1683,7 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.0256783707207232</v>
+        <v>0.0256783706873435</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>53.48114735305222</v>
+        <v>53.48114741638003</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>27.67049570260034</v>
+        <v>27.67049570260033</v>
       </c>
       <c r="J24" s="2" t="n">
         <v>0.6537112824940586</v>
@@ -1736,7 +1736,7 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>-0.0210725773454489</v>
+        <v>-0.0210725773565741</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>55.48243570517651</v>
+        <v>55.48243583662349</v>
       </c>
       <c r="I25" s="2" t="n">
         <v>28.35361368408314</v>
@@ -1789,7 +1789,7 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.0247344406259506</v>
+        <v>0.0247344406281759</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>496.2549857292479</v>
+        <v>496.2549857292478</v>
       </c>
       <c r="E26" s="2" t="n">
         <v>30.9</v>
@@ -1824,10 +1824,10 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>58.45887262375558</v>
+        <v>58.45887266453194</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>18.71366386828052</v>
+        <v>18.713663837435</v>
       </c>
       <c r="J26" s="2" t="n">
         <v>0.7051406157625537</v>
@@ -1842,7 +1842,7 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>0.2561221695984589</v>
+        <v>0.2561221695762053</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>48.82640971135586</v>
+        <v>48.82640981216053</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>12.2744445123444</v>
+        <v>12.2744445331203</v>
       </c>
       <c r="J27" s="2" t="n">
         <v>1.531400252959722</v>
@@ -1930,10 +1930,10 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>49.6890941959791</v>
+        <v>49.68909399118995</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>21.08901632706459</v>
+        <v>21.08901630232535</v>
       </c>
       <c r="J28" s="2" t="n">
         <v>0.7878205253041712</v>
@@ -1948,7 +1948,7 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.0164448750413579</v>
+        <v>0.0164448750747391</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -1983,10 +1983,10 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>42.50966776336448</v>
+        <v>42.50966780455239</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>28.89237810026683</v>
+        <v>28.89237817161342</v>
       </c>
       <c r="J29" s="2" t="n">
         <v>2.508345645706944</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>39.6499231005707</v>
+        <v>39.64992306979794</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>20.79792211131302</v>
+        <v>20.7979221474125</v>
       </c>
       <c r="J30" s="2" t="n">
         <v>0.5862350659408259</v>
@@ -2089,10 +2089,10 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>46.10594747465212</v>
+        <v>46.10594746760585</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>17.46624585831511</v>
+        <v>17.46624590813425</v>
       </c>
       <c r="J31" s="2" t="n">
         <v>0.4436552810998709</v>
@@ -2107,7 +2107,7 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.1259237993221172</v>
+        <v>0.1259237993443784</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>53.5877446750235</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>34.09691412721011</v>
+        <v>34.09691413495643</v>
       </c>
       <c r="J32" s="2" t="n">
         <v>1.795983580426009</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>44.18436452915455</v>
+        <v>44.18436421506431</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>13.92977540369517</v>
+        <v>13.92977588778416</v>
       </c>
       <c r="J33" s="2" t="n">
         <v>1.053801751042616</v>
@@ -2213,7 +2213,7 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>-0.0102843299819899</v>
+        <v>-0.0102843299466756</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
@@ -2248,10 +2248,10 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>36.43831637129214</v>
+        <v>36.43831643053608</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>21.99582910455362</v>
+        <v>21.9958290371751</v>
       </c>
       <c r="J34" s="2" t="n">
         <v>2.528985684292139</v>
@@ -2301,10 +2301,10 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>37.29775226429642</v>
+        <v>37.29775221028437</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>27.13297719712186</v>
+        <v>27.13297722825114</v>
       </c>
       <c r="J35" s="2" t="n">
         <v>0.6178356628006788</v>
@@ -2319,7 +2319,7 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>0.3779994407752971</v>
+        <v>0.377999440552772</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>450.3570762676169</v>
+        <v>450.3570762676171</v>
       </c>
       <c r="E36" s="2" t="n">
         <v>74.5</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>43.20257747606914</v>
+        <v>43.20257743307304</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>8.542082375698199</v>
+        <v>8.542082409251947</v>
       </c>
       <c r="J36" s="2" t="n">
         <v>0.5435439067548555</v>
@@ -2372,7 +2372,7 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-0.0541424027859738</v>
+        <v>-0.0541424028304857</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
@@ -2407,10 +2407,10 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>49.42826941589242</v>
+        <v>49.42826943641698</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>13.55143722092805</v>
+        <v>13.55143726049205</v>
       </c>
       <c r="J37" s="2" t="n">
         <v>0.5977734942476089</v>
@@ -2425,7 +2425,7 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>-0.0857500968731737</v>
+        <v>-0.0857500968843012</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
@@ -2460,7 +2460,7 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>54.70469487406808</v>
+        <v>54.70469492748363</v>
       </c>
       <c r="I38" s="2" t="n">
         <v>22.3018726441397</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>44.72683610069753</v>
+        <v>44.72683614761517</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>18.44940280019104</v>
+        <v>18.4494026846607</v>
       </c>
       <c r="J39" s="2" t="n">
         <v>0.7415643761119077</v>
@@ -2531,7 +2531,7 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>-0.1122256822793139</v>
+        <v>-0.1122256822904404</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
@@ -2566,10 +2566,10 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>57.08322822726369</v>
+        <v>57.08322830207274</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>17.18057368936899</v>
+        <v>17.18057358761949</v>
       </c>
       <c r="J40" s="2" t="n">
         <v>1.201204532330209</v>
@@ -2584,7 +2584,7 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.0574064352045982</v>
+        <v>0.0574064351712171</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
@@ -2622,7 +2622,7 @@
         <v>50.7310841029356</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>12.38310167198658</v>
+        <v>12.38310163212458</v>
       </c>
       <c r="J41" s="2" t="n">
         <v>0.7146941047175062</v>
@@ -2637,7 +2637,7 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>0.0077391385755187</v>
+        <v>0.0077391385710682</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>55.02449391742635</v>
+        <v>55.02449396044642</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>23.67688712688496</v>
+        <v>23.67688712488708</v>
       </c>
       <c r="J42" s="2" t="n">
         <v>0.9556686811682706</v>
@@ -2690,7 +2690,7 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.09503921675873719</v>
+        <v>0.0950392167253578</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
@@ -2725,10 +2725,10 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>23.48532301472335</v>
+        <v>23.48532286123746</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>55.30601215380953</v>
+        <v>55.30601226880396</v>
       </c>
       <c r="J43" s="2" t="n">
         <v>0.7419841596453609</v>
@@ -2743,7 +2743,7 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.0029094900312419</v>
+        <v>0.0029094900534947</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>393.1758889026943</v>
+        <v>393.1758889026947</v>
       </c>
       <c r="E44" s="2" t="n">
         <v>19.5</v>
@@ -2781,7 +2781,7 @@
         <v>35.01010917200365</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>25.93105855792507</v>
+        <v>25.93105855792506</v>
       </c>
       <c r="J44" s="2" t="n">
         <v>2.633623604883756</v>
@@ -2796,7 +2796,7 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>-0.0464793444631961</v>
+        <v>-0.0464793444854534</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>49.18804503133477</v>
+        <v>49.18804492494377</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>12.27872909353246</v>
+        <v>12.27872914352922</v>
       </c>
       <c r="J45" s="2" t="n">
         <v>0.4851515203636359</v>
@@ -2849,7 +2849,7 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.0730598204930125</v>
+        <v>0.0730598205820274</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
@@ -2884,10 +2884,10 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>50.92365550605701</v>
+        <v>50.9236547500019</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>9.806276713361891</v>
+        <v>9.80627596338382</v>
       </c>
       <c r="J46" s="2" t="n">
         <v>0.0747420465119755</v>
@@ -2902,7 +2902,7 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.09611460400455581</v>
+        <v>0.09611460856668</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
@@ -2937,10 +2937,10 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>49.76664279490457</v>
+        <v>49.7666429023317</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>15.48193259133164</v>
+        <v>15.48193259426007</v>
       </c>
       <c r="J47" s="2" t="n">
         <v>0.5075576072771187</v>
@@ -2955,7 +2955,7 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>-0.0126520573069006</v>
+        <v>-0.0126520573291546</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>52.30168129203528</v>
+        <v>52.30168131835046</v>
       </c>
       <c r="I48" s="2" t="n">
         <v>27.20162805373186</v>
@@ -3043,10 +3043,10 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>48.27071856087006</v>
+        <v>48.27071877462282</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>11.9693411348231</v>
+        <v>11.96934108697152</v>
       </c>
       <c r="J49" s="2" t="n">
         <v>0.8735184449598299</v>
@@ -3061,7 +3061,7 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>0.0113185601657682</v>
+        <v>0.0113185601546401</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
@@ -3096,10 +3096,10 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>52.1648936802383</v>
+        <v>52.16489369128615</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>10.57232564303941</v>
+        <v>10.57232564408768</v>
       </c>
       <c r="J50" s="2" t="n">
         <v>0.3884383752219517</v>
@@ -3114,7 +3114,7 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>1.714778827295699</v>
+        <v>1.714778827095411</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>46.5887190325304</v>
+        <v>46.58871902185003</v>
       </c>
       <c r="I51" s="2" t="n">
         <v>24.97273187999811</v>
@@ -3167,7 +3167,7 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-0.0370862846289644</v>
+        <v>-0.0370862846245132</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
@@ -3202,10 +3202,10 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>50.73631477243313</v>
+        <v>50.73631478657666</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>8.566707797494177</v>
+        <v>8.566707766651756</v>
       </c>
       <c r="J52" s="2" t="n">
         <v>0.6607899626004681</v>
@@ -3220,7 +3220,7 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>-0.0144298796478403</v>
+        <v>-0.0144298796367095</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
@@ -3241,7 +3241,7 @@
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>352.4093822999625</v>
+        <v>352.4093822999626</v>
       </c>
       <c r="E53" s="2" t="n">
         <v>7.11</v>
@@ -3255,10 +3255,10 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>50.93823418234832</v>
+        <v>50.93823418011675</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>10.20390864370355</v>
+        <v>10.2039087465847</v>
       </c>
       <c r="J53" s="2" t="n">
         <v>0.1952270638936701</v>
@@ -3273,7 +3273,7 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.0675868625265706</v>
+        <v>0.0675868625376977</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>30.33335353473473</v>
+        <v>30.33335354968206</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>24.70963798295186</v>
+        <v>24.70963799561322</v>
       </c>
       <c r="J54" s="2" t="n">
         <v>0</v>
@@ -3361,10 +3361,10 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>42.42273710004807</v>
+        <v>42.42273716006804</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>9.035857335734343</v>
+        <v>9.035857357254471</v>
       </c>
       <c r="J55" s="2" t="n">
         <v>0.3483373997759351</v>
@@ -3379,7 +3379,7 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>-0.0293021761028913</v>
+        <v>-0.0293021761473972</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
@@ -3400,7 +3400,7 @@
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>344.4726968174039</v>
+        <v>344.4726968174029</v>
       </c>
       <c r="E56" s="2" t="n">
         <v>105.5</v>
@@ -3414,10 +3414,10 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>41.22010908431373</v>
+        <v>41.22010905508024</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>14.01687644298336</v>
+        <v>14.01687649796679</v>
       </c>
       <c r="J56" s="2" t="n">
         <v>1.67872921694417</v>
@@ -3432,7 +3432,7 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-0.3796153903959114</v>
+        <v>-0.3796153901733557</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>48.48313183366961</v>
+        <v>48.4831316874271</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>26.19789054601214</v>
+        <v>26.19789063435394</v>
       </c>
       <c r="J57" s="2" t="n">
         <v>0.3359423949778098</v>
@@ -3485,7 +3485,7 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.0650936252673958</v>
+        <v>0.0650936253230323</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
@@ -3520,10 +3520,10 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>28.35692071737463</v>
+        <v>28.35692068898176</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>27.44815135022232</v>
+        <v>27.44815147606382</v>
       </c>
       <c r="J58" s="2" t="n">
         <v>1.653008422598548</v>
@@ -3559,7 +3559,7 @@
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>337.5014318014991</v>
+        <v>337.5014318015</v>
       </c>
       <c r="E59" s="2" t="n">
         <v>26</v>
@@ -3573,10 +3573,10 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>38.63179023705977</v>
+        <v>38.63179017613456</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>27.71108267960776</v>
+        <v>27.71108271913661</v>
       </c>
       <c r="J59" s="2" t="n">
         <v>0.6761643598881846</v>
@@ -3591,7 +3591,7 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-0.002391576385721</v>
+        <v>-0.0023915763523414</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>337.3024659744194</v>
+        <v>337.3024659744196</v>
       </c>
       <c r="E60" s="2" t="n">
         <v>15.45</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>39.62140690004976</v>
+        <v>39.62140688176712</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>32.55773091442138</v>
+        <v>32.55773091961071</v>
       </c>
       <c r="J60" s="2" t="n">
         <v>0.5852551952054829</v>
@@ -3644,7 +3644,7 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.07935765030684699</v>
+        <v>0.07935765031797359</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>334.2416530707877</v>
+        <v>334.2416530707878</v>
       </c>
       <c r="E61" s="2" t="n">
         <v>32.65</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>50.76748480707426</v>
+        <v>50.76748506969586</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>8.232681516660033</v>
+        <v>8.232681467949597</v>
       </c>
       <c r="J61" s="2" t="n">
         <v>0.7607929230308067</v>
@@ -3697,7 +3697,7 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.0384647182931859</v>
+        <v>0.0384647181819148</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
@@ -3732,10 +3732,10 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>24.76761654329372</v>
+        <v>24.7676165751141</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>24.9465641585789</v>
+        <v>24.94656416567871</v>
       </c>
       <c r="J62" s="2" t="n">
         <v>3.092441738586137</v>
@@ -3750,7 +3750,7 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-0.1118197576025184</v>
+        <v>-0.1118197575913933</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
@@ -3785,10 +3785,10 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>32.41645746766615</v>
+        <v>32.41645751337705</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>19.27713964822369</v>
+        <v>19.27713965175261</v>
       </c>
       <c r="J63" s="2" t="n">
         <v>0.951770542148195</v>
@@ -3803,7 +3803,7 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-0.2440892928555463</v>
+        <v>-0.2440892929890712</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
@@ -3838,10 +3838,10 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>39.89126324080706</v>
+        <v>39.89126313163326</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>16.13051195168057</v>
+        <v>16.13051199636772</v>
       </c>
       <c r="J64" s="2" t="n">
         <v>0.7020971486000142</v>
@@ -3856,7 +3856,7 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-0.1374133380681245</v>
+        <v>-0.1374133378789614</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>322.1183274563284</v>
+        <v>322.1183274563285</v>
       </c>
       <c r="E65" s="2" t="n">
         <v>68.5</v>
@@ -3891,10 +3891,10 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>43.23004444130681</v>
+        <v>43.2300446207012</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>15.93433192821562</v>
+        <v>15.93433202775706</v>
       </c>
       <c r="J65" s="2" t="n">
         <v>0.7089900705847003</v>
@@ -3909,7 +3909,7 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-0.3721517101080017</v>
+        <v>-0.372151710375047</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
@@ -3944,10 +3944,10 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>44.62162323283446</v>
+        <v>44.62162327761597</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>21.31044175539902</v>
+        <v>21.31044177157621</v>
       </c>
       <c r="J66" s="2" t="n">
         <v>0.5345146938859737</v>
@@ -3962,7 +3962,7 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-0.0544585818943868</v>
+        <v>-0.0544585819388959</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
@@ -3983,7 +3983,7 @@
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>320.9136727001994</v>
+        <v>320.9136727002009</v>
       </c>
       <c r="E67" s="2" t="n">
         <v>12.3</v>
@@ -3997,10 +3997,10 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>44.31604735532043</v>
+        <v>44.3160394761975</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>22.81993943831284</v>
+        <v>22.81993927290189</v>
       </c>
       <c r="J67" s="2" t="n">
         <v>0.4719151337708807</v>
@@ -4015,7 +4015,7 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.0012891706281601</v>
+        <v>0.0012891739106651</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
@@ -4050,10 +4050,10 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>43.16358200312141</v>
+        <v>43.16358167791867</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>10.65137082042527</v>
+        <v>10.65137093722135</v>
       </c>
       <c r="J68" s="2" t="n">
         <v>0.8809447083253089</v>
@@ -4068,7 +4068,7 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-0.0169469592001902</v>
+        <v>-0.0169469590221569</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
@@ -4089,7 +4089,7 @@
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>310.4276352766508</v>
+        <v>310.427635276651</v>
       </c>
       <c r="E69" s="2" t="n">
         <v>17.1</v>
@@ -4103,10 +4103,10 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>43.29169746622856</v>
+        <v>43.29169752996959</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>18.6388506235312</v>
+        <v>18.63885062505226</v>
       </c>
       <c r="J69" s="2" t="n">
         <v>0.911360284080754</v>
@@ -4156,10 +4156,10 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>43.14906615127083</v>
+        <v>43.14906605106527</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>23.50223988705314</v>
+        <v>23.50224000727427</v>
       </c>
       <c r="J70" s="2" t="n">
         <v>0.5120523351121652</v>
@@ -4174,7 +4174,7 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.1264880517141436</v>
+        <v>0.1264880517809049</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
@@ -4209,10 +4209,10 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>44.43546668675432</v>
+        <v>44.4354667579651</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>18.87600789052682</v>
+        <v>18.87600785958044</v>
       </c>
       <c r="J71" s="2" t="n">
         <v>0.1499276599040962</v>
@@ -4227,7 +4227,7 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-0.1577845764281358</v>
+        <v>-0.1577845764837742</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
@@ -4248,7 +4248,7 @@
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>297.8901220404103</v>
+        <v>297.8901220404102</v>
       </c>
       <c r="E72" s="2" t="n">
         <v>13.05</v>
@@ -4262,10 +4262,10 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>44.63866022279278</v>
+        <v>44.63866026332624</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>20.77728980728407</v>
+        <v>20.77728986345522</v>
       </c>
       <c r="J72" s="2" t="n">
         <v>0.502963476140964</v>
@@ -4315,10 +4315,10 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>51.5678248157296</v>
+        <v>51.56782484695619</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>12.99633628037481</v>
+        <v>12.99633626789948</v>
       </c>
       <c r="J73" s="2" t="n">
         <v>1.603768348902477</v>
@@ -4333,7 +4333,7 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-0.0309995603814466</v>
+        <v>-0.0309995603703189</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
@@ -4354,7 +4354,7 @@
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>292.9792414255561</v>
+        <v>292.9792414255554</v>
       </c>
       <c r="E74" s="2" t="n">
         <v>699</v>
@@ -4371,7 +4371,7 @@
         <v>44.12876814630479</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>11.31046961010666</v>
+        <v>11.31046964208165</v>
       </c>
       <c r="J74" s="2" t="n">
         <v>0.4262569204174543</v>
@@ -4386,7 +4386,7 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-2.325496132454834</v>
+        <v>-2.325496131564828</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
@@ -4407,7 +4407,7 @@
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>292.2727637231951</v>
+        <v>292.2727637231952</v>
       </c>
       <c r="E75" s="2" t="n">
         <v>276.5</v>
@@ -4421,10 +4421,10 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>27.6006514368144</v>
+        <v>27.6006512046645</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>39.59134505989268</v>
+        <v>39.59134512526497</v>
       </c>
       <c r="J75" s="2" t="n">
         <v>1.101667727907232</v>
@@ -4439,7 +4439,7 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-0.7220464013706298</v>
+        <v>-0.7220463999241034</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
@@ -4474,10 +4474,10 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>39.69797596997519</v>
+        <v>39.6979772051025</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>22.84733814630626</v>
+        <v>22.84733844636558</v>
       </c>
       <c r="J76" s="2" t="n">
         <v>0.4376298873520786</v>
@@ -4492,7 +4492,7 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>0.009058500241062599</v>
+        <v>0.009058499985138401</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
@@ -4527,10 +4527,10 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>48.14675887273457</v>
+        <v>48.14675865393064</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>22.71983757968933</v>
+        <v>22.71983768833963</v>
       </c>
       <c r="J77" s="2" t="n">
         <v>0.5794892233667036</v>
@@ -4545,7 +4545,7 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>0.1215759979187395</v>
+        <v>0.1215759980633953</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
@@ -4583,7 +4583,7 @@
         <v>51.21739120090434</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>11.48208651725725</v>
+        <v>11.4820865086376</v>
       </c>
       <c r="J78" s="2" t="n">
         <v>1.508667725671662</v>
@@ -4633,10 +4633,10 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>36.72531320496911</v>
+        <v>36.72531310545264</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>37.98356660496544</v>
+        <v>37.9835667983133</v>
       </c>
       <c r="J79" s="2" t="n">
         <v>0.7091782403611994</v>
@@ -4651,7 +4651,7 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>0.3264349120216505</v>
+        <v>0.3264349122441907</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
@@ -4686,10 +4686,10 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>42.71665586666957</v>
+        <v>42.71665582985549</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>9.140662893558956</v>
+        <v>9.140662916425883</v>
       </c>
       <c r="J80" s="2" t="n">
         <v>0.918806715129435</v>
@@ -4704,7 +4704,7 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-0.0378001681185071</v>
+        <v>-0.0378001679849754</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
@@ -4739,10 +4739,10 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>50.21515326515548</v>
+        <v>50.2151533295398</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>12.34245617887821</v>
+        <v>12.34245620786279</v>
       </c>
       <c r="J81" s="2" t="n">
         <v>0.4095651925805789</v>
@@ -4792,10 +4792,10 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>45.35370215381646</v>
+        <v>45.35370189206611</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>16.77278616033155</v>
+        <v>16.77278629394617</v>
       </c>
       <c r="J82" s="2" t="n">
         <v>0.4670247023880471</v>
@@ -4810,7 +4810,7 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-0.2187264451033156</v>
+        <v>-0.2187264446582409</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
@@ -4831,7 +4831,7 @@
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>255.2791340115592</v>
+        <v>255.2791340115593</v>
       </c>
       <c r="E83" s="2" t="n">
         <v>6.25</v>
@@ -4845,10 +4845,10 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>31.90709043628356</v>
+        <v>31.90709045807145</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>22.6108859698442</v>
+        <v>22.610885998567</v>
       </c>
       <c r="J83" s="2" t="n">
         <v>1.267694664083302</v>
@@ -4863,7 +4863,7 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-0.010936478126146</v>
+        <v>-0.0109364781328225</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>255.2454065857505</v>
+        <v>255.2454065857506</v>
       </c>
       <c r="E84" s="2" t="n">
         <v>17.45</v>
@@ -4898,10 +4898,10 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>40.38847264881744</v>
+        <v>40.38847240937753</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>32.06027476096221</v>
+        <v>32.06027486959128</v>
       </c>
       <c r="J84" s="2" t="n">
         <v>0.6225557950428553</v>
@@ -4916,7 +4916,7 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-0.0039314140558742</v>
+        <v>-0.0039314138842467</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
@@ -4937,7 +4937,7 @@
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>251.6014864706743</v>
+        <v>251.6014864706753</v>
       </c>
       <c r="E85" s="2" t="n">
         <v>66</v>
@@ -4951,10 +4951,10 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>48.37591118037257</v>
+        <v>48.37591114242193</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>12.05625701010428</v>
+        <v>12.05625710173019</v>
       </c>
       <c r="J85" s="2" t="n">
         <v>0.2763589828495598</v>
@@ -4969,7 +4969,7 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-0.125174743737088</v>
+        <v>-0.1251747436703258</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
@@ -5004,10 +5004,10 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>39.6541399191126</v>
+        <v>39.65414005025227</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>7.558030916863396</v>
+        <v>7.558030902244351</v>
       </c>
       <c r="J86" s="2" t="n">
         <v>2.986749443468509</v>
@@ -5022,7 +5022,7 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>0.0146174883849338</v>
+        <v>0.0146174883292986</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
@@ -5060,7 +5060,7 @@
         <v>33.06635877516952</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>23.33689467604703</v>
+        <v>23.33689468688239</v>
       </c>
       <c r="J87" s="2" t="n">
         <v>0.4179182929817769</v>
@@ -5110,10 +5110,10 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>48.71433743579543</v>
+        <v>48.71433746003079</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>5.930345847115438</v>
+        <v>5.930345877287301</v>
       </c>
       <c r="J88" s="2" t="n">
         <v>0.436274081950618</v>
@@ -5128,7 +5128,7 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>0.0415502904453151</v>
+        <v>0.0415502904341879</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
@@ -5166,7 +5166,7 @@
         <v>43.88170428445039</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>15.08183058431626</v>
+        <v>15.08183060356054</v>
       </c>
       <c r="J89" s="2" t="n">
         <v>0.5186073575128568</v>
@@ -5181,7 +5181,7 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>0.0155526809358521</v>
+        <v>0.0155526809447538</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
@@ -5216,10 +5216,10 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>42.16577189361502</v>
+        <v>42.16577188899697</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>10.29497635124557</v>
+        <v>10.29497638536218</v>
       </c>
       <c r="J90" s="2" t="n">
         <v>0.168613957688645</v>
@@ -5234,7 +5234,7 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>0.0310783092013129</v>
+        <v>0.0310783091946367</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>49.16387774062459</v>
+        <v>49.16387776089812</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>14.44930207460586</v>
+        <v>14.44930207468676</v>
       </c>
       <c r="J91" s="2" t="n">
         <v>1.351277911539894</v>
@@ -5322,10 +5322,10 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>34.03165134729996</v>
+        <v>34.03165139728567</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>24.15595550882902</v>
+        <v>24.15595555901442</v>
       </c>
       <c r="J92" s="2" t="n">
         <v>0.2697946046931946</v>
@@ -5340,7 +5340,7 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-0.0216342541357427</v>
+        <v>-0.021634254146869</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
@@ -5375,7 +5375,7 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>32.59704687693366</v>
+        <v>32.59704685672858</v>
       </c>
       <c r="I93" s="2" t="n">
         <v>29.78140838246116</v>
@@ -5428,10 +5428,10 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>46.59781347622856</v>
+        <v>46.59781340263403</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>14.5512646240608</v>
+        <v>14.55126467028614</v>
       </c>
       <c r="J94" s="2" t="n">
         <v>0.5180395055277867</v>
@@ -5446,7 +5446,7 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-0.241526160709038</v>
+        <v>-0.2415261605977617</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>43.75689456264242</v>
+        <v>43.7568946610978</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>14.52606955811724</v>
+        <v>14.52606964115181</v>
       </c>
       <c r="J95" s="2" t="n">
         <v>1.061136792964763</v>
@@ -5499,7 +5499,7 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-0.0083989865191862</v>
+        <v>-0.0083989865303126</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
@@ -5534,10 +5534,10 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>48.6457856648475</v>
+        <v>48.64578571277686</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>12.18296464062828</v>
+        <v>12.18296468119942</v>
       </c>
       <c r="J96" s="2" t="n">
         <v>0.2249250096795675</v>
@@ -5552,7 +5552,7 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-0.08381279588639851</v>
+        <v>-0.08381279595315751</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
@@ -5587,10 +5587,10 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>33.17979786824418</v>
+        <v>33.17979777692447</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>8.769809602556821</v>
+        <v>8.769809536284505</v>
       </c>
       <c r="J97" s="2" t="n">
         <v>0.7535309221377681</v>
@@ -5605,7 +5605,7 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-0.4561794846315825</v>
+        <v>-0.4561794838526847</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
@@ -5640,10 +5640,10 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>40.61848534278261</v>
+        <v>40.61848539298406</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>17.86580193502385</v>
+        <v>17.86580194258671</v>
       </c>
       <c r="J98" s="2" t="n">
         <v>0.4362253128082805</v>
@@ -5658,7 +5658,7 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>0.0126355083886178</v>
+        <v>0.0126355083663625</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
@@ -5696,7 +5696,7 @@
         <v>50.91200446564194</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>8.92065751425168</v>
+        <v>8.92065743071935</v>
       </c>
       <c r="J99" s="2" t="n">
         <v>0.603459583538285</v>
@@ -5711,7 +5711,7 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>0.3059918046846929</v>
+        <v>0.3059918036975808</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
@@ -5746,10 +5746,10 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>34.86046120086584</v>
+        <v>34.8604613306469</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>32.47825076977574</v>
+        <v>32.47825078960295</v>
       </c>
       <c r="J100" s="2" t="n">
         <v>0.7728841266485443</v>
@@ -5764,7 +5764,7 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>0.002911906848098</v>
+        <v>0.0029119068035889</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
@@ -5802,7 +5802,7 @@
         <v>41.08444409117836</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>10.97575308408577</v>
+        <v>10.97575311375755</v>
       </c>
       <c r="J101" s="2" t="n">
         <v>0.8187801994017417</v>
@@ -5817,7 +5817,7 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>0.0050552602111418</v>
+        <v>0.0050552602222698</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
@@ -5852,7 +5852,7 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>39.5403746782918</v>
+        <v>39.5403746354615</v>
       </c>
       <c r="I102" s="2" t="n">
         <v>23.16158012845588</v>
@@ -5870,7 +5870,7 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.0581086230829653</v>
+        <v>-0.0581086232164911</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
@@ -5891,7 +5891,7 @@
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>210.8729195606531</v>
+        <v>210.8729195606529</v>
       </c>
       <c r="E103" s="2" t="n">
         <v>23.05</v>
@@ -5905,10 +5905,10 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>45.25963943182494</v>
+        <v>45.25963941071828</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>5.119036154578149</v>
+        <v>5.119036158802952</v>
       </c>
       <c r="J103" s="2" t="n">
         <v>0.8622069614414106</v>
@@ -5923,7 +5923,7 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-0.0033726784687696</v>
+        <v>-0.0033726784242615</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
@@ -5958,10 +5958,10 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>50.43547673679654</v>
+        <v>50.43547668344164</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>18.06665908503258</v>
+        <v>18.06665903120349</v>
       </c>
       <c r="J104" s="2" t="n">
         <v>0.9288049767465556</v>
@@ -5997,7 +5997,7 @@
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>194.2179619016106</v>
+        <v>194.2179619016094</v>
       </c>
       <c r="E105" s="2" t="n">
         <v>64.40000000000001</v>
@@ -6011,7 +6011,7 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>51.18018451381249</v>
+        <v>51.1801845104879</v>
       </c>
       <c r="I105" s="2" t="n">
         <v>21.542490833729</v>
@@ -6029,7 +6029,7 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-1.184543157539203</v>
+        <v>-1.184543157516954</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
@@ -6064,10 +6064,10 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>42.75937508015001</v>
+        <v>42.75937494302369</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>16.36644321871258</v>
+        <v>16.36644328919786</v>
       </c>
       <c r="J106" s="2" t="n">
         <v>1.081609927212568</v>
@@ -6082,7 +6082,7 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>0.0069930215937528</v>
+        <v>0.0069930216382601</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
@@ -6117,10 +6117,10 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>45.46547030186201</v>
+        <v>45.46547029883565</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>13.19563541064757</v>
+        <v>13.19563546358064</v>
       </c>
       <c r="J107" s="2" t="n">
         <v>0.5325164438786336</v>
@@ -6156,7 +6156,7 @@
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>177.8432355317164</v>
+        <v>177.8432355317171</v>
       </c>
       <c r="E108" s="2" t="n">
         <v>196</v>
@@ -6170,10 +6170,10 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>43.30531215740378</v>
+        <v>43.3053121204459</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>10.00399064412504</v>
+        <v>10.00399061324159</v>
       </c>
       <c r="J108" s="2" t="n">
         <v>0.425144086768141</v>
@@ -6188,7 +6188,7 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.54228181406623</v>
+        <v>-0.5422818135098741</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
@@ -6223,10 +6223,10 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>48.39437996819087</v>
+        <v>48.39437984241511</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>12.54145300237842</v>
+        <v>12.5414530121041</v>
       </c>
       <c r="J109" s="2" t="n">
         <v>0.5535224586928081</v>
@@ -6241,7 +6241,7 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>0.0512900796150477</v>
+        <v>0.051290079603922</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
@@ -6276,10 +6276,10 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>52.77989777541445</v>
+        <v>52.77989777384564</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>9.1671226089423</v>
+        <v>9.167122732721641</v>
       </c>
       <c r="J110" s="2" t="n">
         <v>0.4798771552722107</v>
@@ -6329,10 +6329,10 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>45.75353411473413</v>
+        <v>45.75353481040914</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>11.43605779883075</v>
+        <v>11.43605780109266</v>
       </c>
       <c r="J111" s="2" t="n">
         <v>0.0001400550416313</v>
@@ -6382,10 +6382,10 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>51.91879873819772</v>
+        <v>51.91879876999717</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>19.44384807457648</v>
+        <v>19.44384805724503</v>
       </c>
       <c r="J112" s="2" t="n">
         <v>0.2236906510034263</v>
@@ -6400,7 +6400,7 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>0.040437559178269</v>
+        <v>0.0404375591337598</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
@@ -6435,10 +6435,10 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>47.78896365929295</v>
+        <v>47.78896380223252</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>15.68770203533845</v>
+        <v>15.6877020822982</v>
       </c>
       <c r="J113" s="2" t="n">
         <v>1.138063168865906</v>
@@ -6453,7 +6453,7 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>0.0102298858998013</v>
+        <v>0.0102298857662753</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
@@ -6488,10 +6488,10 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>32.86232830231734</v>
+        <v>32.86232835427593</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>19.10831852076622</v>
+        <v>19.1083185270153</v>
       </c>
       <c r="J114" s="2" t="n">
         <v>0.3016058633221153</v>
@@ -6506,7 +6506,7 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-0.1218205302602301</v>
+        <v>-0.1218205302713583</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
@@ -6541,10 +6541,10 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>49.90280756175169</v>
+        <v>49.9028075076608</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>12.69467972535677</v>
+        <v>12.69467974136995</v>
       </c>
       <c r="J115" s="2" t="n">
         <v>1.087615949355959</v>
@@ -6559,7 +6559,7 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-0.0005648758012771</v>
+        <v>-0.0005648757901528</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
@@ -6594,10 +6594,10 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>38.80466804510702</v>
+        <v>38.80466817390331</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>9.51976021130945</v>
+        <v>9.519760325191257</v>
       </c>
       <c r="J116" s="2" t="n">
         <v>0.9554569055577288</v>
@@ -6612,7 +6612,7 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>0.0102867785153978</v>
+        <v>0.0102867784909188</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
@@ -6647,10 +6647,10 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>41.02453300258299</v>
+        <v>41.02453308743376</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>10.16589351099681</v>
+        <v>10.16589345732232</v>
       </c>
       <c r="J117" s="2" t="n">
         <v>0.1011474815970939</v>
@@ -6665,7 +6665,7 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>-0.0017563047101163</v>
+        <v>-0.0017563047323714</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
@@ -6700,10 +6700,10 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>36.77541204876096</v>
+        <v>36.7754120780831</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>23.03727374614221</v>
+        <v>23.03727390729559</v>
       </c>
       <c r="J118" s="2" t="n">
         <v>0.1997971702293157</v>
@@ -6718,7 +6718,7 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>-0.0115572104211656</v>
+        <v>-0.0115572103766573</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
@@ -6753,10 +6753,10 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>37.80698450167327</v>
+        <v>37.80698417416073</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>17.25404851467422</v>
+        <v>17.25404869356028</v>
       </c>
       <c r="J119" s="2" t="n">
         <v>0.09485171628344451</v>
@@ -6771,7 +6771,7 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>-0.0140613970190381</v>
+        <v>-0.0140613969411473</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
@@ -6806,10 +6806,10 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>39.10305957349571</v>
+        <v>39.10305949766703</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>15.84860774067127</v>
+        <v>15.84860767673352</v>
       </c>
       <c r="J120" s="2" t="n">
         <v>0.2898815301299903</v>
@@ -6824,7 +6824,7 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>0.06391953048078711</v>
+        <v>0.06391953056980711</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
@@ -6845,7 +6845,7 @@
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>150.6907412260264</v>
+        <v>150.6907412260263</v>
       </c>
       <c r="E121" s="2" t="n">
         <v>79.59999999999999</v>
@@ -6859,10 +6859,10 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>41.33665306039034</v>
+        <v>41.33665354397382</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>10.76942234848532</v>
+        <v>10.76942273546453</v>
       </c>
       <c r="J121" s="2" t="n">
         <v>0.5036580712732786</v>
@@ -6877,7 +6877,7 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>0.1293157691710231</v>
+        <v>0.1293157696161082</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
@@ -6898,7 +6898,7 @@
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>147.7983562297197</v>
+        <v>147.7983562297198</v>
       </c>
       <c r="E122" s="2" t="n">
         <v>9.19</v>
@@ -6912,10 +6912,10 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>46.17349648567914</v>
+        <v>46.17349666955876</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>8.802496472927102</v>
+        <v>8.802496467773832</v>
       </c>
       <c r="J122" s="2" t="n">
         <v>0.3445227478682101</v>
@@ -6930,7 +6930,7 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>0.005949713040227</v>
+        <v>0.0059497129957167</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
@@ -6951,7 +6951,7 @@
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>143.2164431712961</v>
+        <v>143.216443171296</v>
       </c>
       <c r="E123" s="2" t="n">
         <v>14.35</v>
@@ -6965,10 +6965,10 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>47.14649688258773</v>
+        <v>47.14649684961105</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>11.92050045338421</v>
+        <v>11.92050058084785</v>
       </c>
       <c r="J123" s="2" t="n">
         <v>0.5152589055244483</v>
@@ -7018,10 +7018,10 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>43.64610464171341</v>
+        <v>43.64610452882009</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>19.23217675365634</v>
+        <v>19.2321769938357</v>
       </c>
       <c r="J124" s="2" t="n">
         <v>0.1051216414652538</v>
@@ -7036,7 +7036,7 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>0.0159319405502945</v>
+        <v>0.0159319406615676</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>36.18091053745876</v>
+        <v>36.18091049785818</v>
       </c>
       <c r="I125" s="2" t="n">
         <v>9.354981228073022</v>
@@ -7089,7 +7089,7 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>-0.0036221741302361</v>
+        <v>-0.0036221741079822</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
@@ -7127,7 +7127,7 @@
         <v>39.06292270622599</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>9.452739850796</v>
+        <v>9.452739850795997</v>
       </c>
       <c r="J126" s="2" t="n">
         <v>0.7371579717980277</v>
@@ -7142,7 +7142,7 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>-0.0005736163092595001</v>
+        <v>-0.000573616311485</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
@@ -7177,10 +7177,10 @@
         <v>0</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>50.927326741284</v>
+        <v>50.92732666269455</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>10.55419107618756</v>
+        <v>10.55419110475697</v>
       </c>
       <c r="J127" s="2" t="n">
         <v>0.7333678287830576</v>
@@ -7195,7 +7195,7 @@
         <v>-1</v>
       </c>
       <c r="N127" s="2" t="n">
-        <v>-0.0101972522932754</v>
+        <v>-0.0101972522821483</v>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
@@ -7230,10 +7230,10 @@
         <v>0</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>39.96116754927892</v>
+        <v>39.9611678999597</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>18.30873243307893</v>
+        <v>18.30873238528409</v>
       </c>
       <c r="J128" s="2" t="n">
         <v>0.5127334465195246</v>
@@ -7286,7 +7286,7 @@
         <v>41.89733806673743</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>14.10139034621174</v>
+        <v>14.10139043644395</v>
       </c>
       <c r="J129" s="2" t="n">
         <v>0.9779548285610944</v>
@@ -7301,7 +7301,7 @@
         <v>-1</v>
       </c>
       <c r="N129" s="2" t="n">
-        <v>-0.0484924270252753</v>
+        <v>-0.0484924269807692</v>
       </c>
       <c r="O129" s="2" t="inlineStr">
         <is>
@@ -7322,7 +7322,7 @@
         <v/>
       </c>
       <c r="D130" s="2" t="n">
-        <v>89.49831170708893</v>
+        <v>89.49831170708894</v>
       </c>
       <c r="E130" s="2" t="n">
         <v>45.6</v>
@@ -7339,7 +7339,7 @@
         <v>49.14989578507964</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>13.93374915212161</v>
+        <v>13.93374908496215</v>
       </c>
       <c r="J130" s="2" t="n">
         <v>0.7975212146144058</v>
@@ -7392,7 +7392,7 @@
         <v>42.81461527802914</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>15.55587129457165</v>
+        <v>15.55587131983602</v>
       </c>
       <c r="J131" s="2" t="n">
         <v>0.5619201813244366</v>
@@ -7442,10 +7442,10 @@
         <v>0</v>
       </c>
       <c r="H132" s="2" t="n">
-        <v>51.74505581842296</v>
+        <v>51.74505590915226</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>11.7786327326755</v>
+        <v>11.77863273267551</v>
       </c>
       <c r="J132" s="2" t="n">
         <v>0.6524428229882353</v>
@@ -7460,7 +7460,7 @@
         <v>-1</v>
       </c>
       <c r="N132" s="2" t="n">
-        <v>0.0160344867030118</v>
+        <v>0.0160344866918867</v>
       </c>
       <c r="O132" s="2" t="inlineStr">
         <is>
@@ -7498,7 +7498,7 @@
         <v>44.53314504609418</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>12.80569386850856</v>
+        <v>12.8056938969914</v>
       </c>
       <c r="J133" s="2" t="n">
         <v>0.2469258623831483</v>
